--- a/Data/Hero/角色列表.xlsx
+++ b/Data/Hero/角色列表.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\英雄相关\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\Data\Hero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B90FD37-BAE4-49BE-B457-998DDD975E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DD762E-1906-4E4E-BCE0-303B4B401295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9915" yWindow="4485" windowWidth="28800" windowHeight="15645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="4650" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
-    <sheet name="词条解释" sheetId="4" r:id="rId2"/>
+    <sheet name="新角色畅想" sheetId="6" r:id="rId2"/>
     <sheet name="数据统计" sheetId="5" r:id="rId3"/>
-    <sheet name="平衡调整" sheetId="2" r:id="rId4"/>
+    <sheet name="词条解释" sheetId="4" r:id="rId4"/>
+    <sheet name="平衡调整" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">角色列表!$A$1:$R$53</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="239">
   <si>
     <t>No.</t>
   </si>
@@ -198,9 +199,6 @@
     <t>赏金猎人</t>
   </si>
   <si>
-    <t>嘲讽</t>
-  </si>
-  <si>
     <t>超新星</t>
   </si>
   <si>
@@ -228,9 +226,6 @@
     <t>战锤</t>
   </si>
   <si>
-    <t>毒蛇</t>
-  </si>
-  <si>
     <t>雪拳</t>
   </si>
   <si>
@@ -316,9 +311,6 @@
   </si>
   <si>
     <t>所有负面效果对其无效，每受到一次负面效果攻击，攻击力+1，持续到我方回合结束。</t>
-  </si>
-  <si>
-    <t>能施加异常状态的英雄</t>
   </si>
   <si>
     <t>坠炮手</t>
@@ -489,10 +481,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>能麻痹的英雄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>能提供攻击力加成的角色
 能使敌人位移的角色</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -682,10 +670,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>圣光</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>没有特殊注明的所有角色的移动力都是2，射程都是1。</t>
   </si>
   <si>
@@ -2379,15 +2363,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>远程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>远程
-后勤</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>能使敌人位移的角色，除了暗域</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2444,6 +2419,92 @@
   </si>
   <si>
     <t>己方回合开始时，在战场中的空地随机放置两个随机的增益道具，生成增益道具只能我方拾取，对方拾取则消失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语义伙伴</t>
+  </si>
+  <si>
+    <t>暗域、傀儡师、超新星、长角、血锁</t>
+  </si>
+  <si>
+    <t>白游侠、烛火、长剑、红帽、末日、死灵法师、超新星</t>
+  </si>
+  <si>
+    <t>白游侠、末日、坠炮手、宿魂、涌电技师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>塔盾、装甲堡垒、复仇者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰祭司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬉皮死神×3、炸弹人×3、烛火×3</t>
+  </si>
+  <si>
+    <t>嬉皮死神×3、烛火×1、炸弹人×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死灵法师、嬉皮死神、长角、小阴影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬉皮死神×3、烛火×2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬉皮死神×3、烛火×1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇淑女、白游侠、小阴影、烛火、长剑、赏金猎人、圣光、复仇者、暗域、嬉皮死神、长角、沉默术士、黄金矿工、风语者、宿魂、共鸣者、荆棘树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傀儡师×3、超新星×3、暗域×3、长角、血锁×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烈焰祭司×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇淑女、战锤、雪拳、白游侠、沉默术士、猎颅者、巨剑、宿魂</t>
+  </si>
+  <si>
+    <t>傀儡师、医护兵、影丸、德鲁伊、火枪手、白游侠、烈焰祭司、赏金猎人、超新星、死灵法师、沉默术士、炸弹人、风语者、坠炮手、烛火、末日、涌电技师</t>
+  </si>
+  <si>
+    <t>塔盾、巨剑、独脚龟、圣光、复仇者、大骑士、战锤、雪拳、梅林、负墟、装甲堡垒、荆棘树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇淑女、烛火、圣光、复仇者、暗域、古灵精怪、嬉皮死神、涌电技师、红帽、宿魂、共鸣者、荆棘树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影丸、烈焰祭司、沉默术士、风语者、坠炮手、涌电技师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼠队长、影丸、火枪手、古拉博士、红帽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狗头军师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我方回合中，站在狗头军师附近的队友</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2683,7 +2744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2761,6 +2822,12 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2781,9 +2848,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3065,7 +3129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="7" bestFit="1" customWidth="1"/>
@@ -3074,17 +3138,22 @@
     <col min="4" max="6" width="9" style="7"/>
     <col min="7" max="7" width="34.375" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.25" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="9" style="7"/>
+    <col min="9" max="9" width="22.875" style="27" customWidth="1"/>
+    <col min="10" max="10" width="9" style="7"/>
+    <col min="11" max="11" width="9" style="7" customWidth="1"/>
+    <col min="12" max="13" width="9" style="7"/>
     <col min="14" max="14" width="10.5" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="7"/>
+    <col min="15" max="18" width="9" style="7"/>
+    <col min="19" max="19" width="28.125" style="27" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -3114,33 +3183,36 @@
         <v>9</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="M1" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="N1" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>123</v>
-      </c>
       <c r="R1" s="14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="S1" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>10</v>
@@ -3162,11 +3234,11 @@
       <c r="J2" s="9"/>
       <c r="K2" s="9"/>
       <c r="L2" s="10">
-        <f>D2*2.2+E2*0.45</f>
+        <f t="shared" ref="L2:L33" si="0">D2*2.2+E2*0.45</f>
         <v>18.75</v>
       </c>
       <c r="M2" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
+        <f t="shared" ref="M2:M33" si="1">SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F2)),-1,0), IF(ISNUMBER(SEARCH("后勤",F2)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N2" s="10">
@@ -3178,19 +3250,19 @@
       </c>
       <c r="P2" s="10"/>
       <c r="Q2" s="10">
-        <f>L2+M2+O2+P2</f>
+        <f t="shared" ref="Q2:Q33" si="2">L2+M2+O2+P2</f>
         <v>18.75</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="69" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="69" x14ac:dyDescent="0.2">
       <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>13</v>
@@ -3205,7 +3277,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>15</v>
@@ -3214,11 +3286,11 @@
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
       <c r="L3" s="10">
-        <f>D3*2.2+E3*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.200000000000001</v>
       </c>
       <c r="M3" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F3)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F3)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F3)),-1,0), IF(ISNUMBER(SEARCH("后勤",F3)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N3" s="10">
@@ -3232,19 +3304,22 @@
         <v>1</v>
       </c>
       <c r="Q3" s="10">
-        <f>L3+M3+O3+P3</f>
+        <f t="shared" si="2"/>
         <v>17.700000000000003</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>16</v>
@@ -3260,19 +3335,19 @@
         <v>17</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="J4" s="12" t="s">
-        <v>127</v>
+      <c r="I4" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" t="s">
+        <v>63</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="10">
-        <f>D4*2.2+E4*0.45</f>
+        <f t="shared" si="0"/>
         <v>11.650000000000002</v>
       </c>
       <c r="M4" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F4)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F4)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F4)),-1,0), IF(ISNUMBER(SEARCH("后勤",F4)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N4" s="10">
@@ -3284,19 +3359,22 @@
       </c>
       <c r="P4" s="10"/>
       <c r="Q4" s="10">
-        <f>L4+M4+O4+P4</f>
+        <f t="shared" si="2"/>
         <v>18.250000000000004</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S4" s="27" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>18</v>
@@ -3316,11 +3394,11 @@
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="10">
-        <f>D5*2.2+E5*0.45</f>
+        <f t="shared" si="0"/>
         <v>16.899999999999999</v>
       </c>
       <c r="M5" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F5)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F5)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F5)),-1,0), IF(ISNUMBER(SEARCH("后勤",F5)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N5" s="10">
@@ -3332,19 +3410,19 @@
       </c>
       <c r="P5" s="10"/>
       <c r="Q5" s="10">
-        <f>L5+M5+O5+P5</f>
+        <f t="shared" si="2"/>
         <v>18.399999999999999</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>19</v>
@@ -3359,20 +3437,19 @@
         <v>20</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="9"/>
       <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
       <c r="L6" s="10">
-        <f>D6*2.2+E6*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.150000000000002</v>
       </c>
       <c r="M6" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F6)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F6)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F6)),-1,0), IF(ISNUMBER(SEARCH("后勤",F6)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N6" s="10">
@@ -3384,19 +3461,22 @@
       </c>
       <c r="P6" s="10"/>
       <c r="Q6" s="10">
-        <f>L6+M6+O6+P6</f>
+        <f t="shared" si="2"/>
         <v>17.350000000000001</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S6" s="27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>22</v>
@@ -3408,7 +3488,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>23</v>
@@ -3420,11 +3500,11 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="10">
-        <f>D7*2.2+E7*0.45</f>
+        <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="M7" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F7)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F7)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F7)),-1,0), IF(ISNUMBER(SEARCH("后勤",F7)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N7" s="10">
@@ -3436,19 +3516,20 @@
       </c>
       <c r="P7" s="10"/>
       <c r="Q7" s="10">
-        <f>L7+M7+O7+P7</f>
+        <f t="shared" si="2"/>
         <v>16.650000000000002</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S7" s="9"/>
+    </row>
+    <row r="8" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>25</v>
@@ -3460,7 +3541,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="9" t="s">
@@ -3470,11 +3551,11 @@
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="10">
-        <f>D8*2.2+E8*0.45</f>
+        <f t="shared" si="0"/>
         <v>17.3</v>
       </c>
       <c r="M8" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F8)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F8)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F8)),-1,0), IF(ISNUMBER(SEARCH("后勤",F8)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N8" s="10"/>
@@ -3484,19 +3565,20 @@
       </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10">
-        <f>L8+M8+O8+P8</f>
+        <f t="shared" si="2"/>
         <v>18.8</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="S8" s="9"/>
+    </row>
+    <row r="9" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>27</v>
@@ -3511,7 +3593,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
@@ -3520,11 +3602,11 @@
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="10">
-        <f>D9*2.2+E9*0.45</f>
+        <f t="shared" si="0"/>
         <v>13.4</v>
       </c>
       <c r="M9" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F9)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F9)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F9)),-1,0), IF(ISNUMBER(SEARCH("后勤",F9)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N9" s="10">
@@ -3536,19 +3618,22 @@
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10">
-        <f>L9+M9+O9+P9</f>
+        <f t="shared" si="2"/>
         <v>15.200000000000001</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S9" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>29</v>
@@ -3568,11 +3653,11 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="10">
-        <f>D10*2.2+E10*0.45</f>
+        <f t="shared" si="0"/>
         <v>17.8</v>
       </c>
       <c r="M10" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F10)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F10)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F10)),-1,0), IF(ISNUMBER(SEARCH("后勤",F10)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N10" s="10"/>
@@ -3582,19 +3667,19 @@
       </c>
       <c r="P10" s="10"/>
       <c r="Q10" s="10">
-        <f>L10+M10+O10+P10</f>
+        <f t="shared" si="2"/>
         <v>17.8</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>30</v>
@@ -3606,7 +3691,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>31</v>
@@ -3618,11 +3703,11 @@
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="10">
-        <f>D11*2.2+E11*0.45</f>
+        <f t="shared" si="0"/>
         <v>12.950000000000001</v>
       </c>
       <c r="M11" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F11)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F11)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F11)),-1,0), IF(ISNUMBER(SEARCH("后勤",F11)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N11" s="10">
@@ -3634,19 +3719,22 @@
       </c>
       <c r="P11" s="10"/>
       <c r="Q11" s="10">
-        <f>L11+M11+O11+P11</f>
+        <f t="shared" si="2"/>
         <v>18.850000000000001</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S11" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>32</v>
@@ -3668,11 +3756,11 @@
       <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="10">
-        <f>D12*2.2+E12*0.45</f>
+        <f t="shared" si="0"/>
         <v>20.2</v>
       </c>
       <c r="M12" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F12)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F12)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F12)),-1,0), IF(ISNUMBER(SEARCH("后勤",F12)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N12" s="10">
@@ -3684,19 +3772,19 @@
       </c>
       <c r="P12" s="10"/>
       <c r="Q12" s="10">
-        <f>L12+M12+O12+P12</f>
+        <f t="shared" si="2"/>
         <v>19.2</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>35</v>
@@ -3718,11 +3806,11 @@
       <c r="J13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="10">
-        <f>D13*2.2+E13*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.200000000000001</v>
       </c>
       <c r="M13" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F13)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F13)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F13)),-1,0), IF(ISNUMBER(SEARCH("后勤",F13)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N13" s="10">
@@ -3734,19 +3822,19 @@
       </c>
       <c r="P13" s="10"/>
       <c r="Q13" s="10">
-        <f>L13+M13+O13+P13</f>
+        <f t="shared" si="2"/>
         <v>18.600000000000001</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>38</v>
@@ -3766,11 +3854,11 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="10">
-        <f>D14*2.2+E14*0.45</f>
+        <f t="shared" si="0"/>
         <v>19.25</v>
       </c>
       <c r="M14" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F14)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F14)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F14)),-1,0), IF(ISNUMBER(SEARCH("后勤",F14)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N14" s="10">
@@ -3782,19 +3870,19 @@
       </c>
       <c r="P14" s="10"/>
       <c r="Q14" s="10">
-        <f>L14+M14+O14+P14</f>
+        <f t="shared" si="2"/>
         <v>18.25</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>39</v>
@@ -3816,11 +3904,11 @@
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="10">
-        <f>D15*2.2+E15*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.55</v>
       </c>
       <c r="M15" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F15)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F15)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F15)),-1,0), IF(ISNUMBER(SEARCH("后勤",F15)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N15" s="10">
@@ -3832,19 +3920,20 @@
       </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10">
-        <f>L15+M15+O15+P15</f>
+        <f t="shared" si="2"/>
         <v>17.350000000000001</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S15" s="9"/>
+    </row>
+    <row r="16" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="9">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>42</v>
@@ -3868,11 +3957,11 @@
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="10">
-        <f>D16*2.2+E16*0.45</f>
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
       <c r="M16" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F16)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F16)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F16)),-1,0), IF(ISNUMBER(SEARCH("后勤",F16)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N16" s="10">
@@ -3884,19 +3973,20 @@
       </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10">
-        <f>L16+M16+O16+P16</f>
+        <f t="shared" si="2"/>
         <v>19.5</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S16" s="12"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>44</v>
@@ -3918,11 +4008,11 @@
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="10">
-        <f>D17*2.2+E17*0.45</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="M17" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F17)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F17)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F17)),-1,0), IF(ISNUMBER(SEARCH("后勤",F17)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N17" s="10">
@@ -3934,19 +4024,19 @@
       </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10">
-        <f>L17+M17+O17+P17</f>
+        <f t="shared" si="2"/>
         <v>18.7</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A18" s="9">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>47</v>
@@ -3958,23 +4048,23 @@
         <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>48</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="10">
-        <f>D18*2.2+E18*0.45</f>
+        <f t="shared" si="0"/>
         <v>14.25</v>
       </c>
       <c r="M18" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F18)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F18)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F18)),-1,0), IF(ISNUMBER(SEARCH("后勤",F18)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
       <c r="N18" s="10">
@@ -3986,19 +4076,22 @@
       </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10">
-        <f>L18+M18+O18+P18</f>
+        <f t="shared" si="2"/>
         <v>21.15</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S18" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>49</v>
@@ -4022,11 +4115,11 @@
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="10">
-        <f>D19*2.2+E19*0.45</f>
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
       <c r="M19" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F19)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F19)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F19)),-1,0), IF(ISNUMBER(SEARCH("后勤",F19)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N19" s="10">
@@ -4038,19 +4131,22 @@
       </c>
       <c r="P19" s="10"/>
       <c r="Q19" s="10">
-        <f>L19+M19+O19+P19</f>
+        <f t="shared" si="2"/>
         <v>20.6</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S19" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>51</v>
@@ -4074,11 +4170,11 @@
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="10">
-        <f>D20*2.2+E20*0.45</f>
+        <f t="shared" si="0"/>
         <v>10.3</v>
       </c>
       <c r="M20" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F20)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F20)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F20)),-1,0), IF(ISNUMBER(SEARCH("后勤",F20)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N20" s="10">
@@ -4090,19 +4186,22 @@
       </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="10">
-        <f>L20+M20+O20+P20</f>
+        <f t="shared" si="2"/>
         <v>16.900000000000002</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S20" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="57" x14ac:dyDescent="0.2">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>54</v>
@@ -4114,25 +4213,25 @@
         <v>19</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>55</v>
+      <c r="I21" s="28" t="s">
+        <v>233</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="10">
-        <f>D21*2.2+E21*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.150000000000002</v>
       </c>
       <c r="M21" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F21)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F21)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F21)),-1,0), IF(ISNUMBER(SEARCH("后勤",F21)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N21" s="10">
@@ -4144,22 +4243,23 @@
       </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10">
-        <f>L21+M21+O21+P21</f>
+        <f t="shared" si="2"/>
         <v>19.550000000000004</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S21" s="9"/>
+    </row>
+    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="9">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D22" s="9">
         <v>3</v>
@@ -4171,20 +4271,19 @@
         <v>20</v>
       </c>
       <c r="G22" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
       <c r="L22" s="10">
-        <f>D22*2.2+E22*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.150000000000002</v>
       </c>
       <c r="M22" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F22)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F22)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F22)),-1,0), IF(ISNUMBER(SEARCH("后勤",F22)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N22" s="10">
@@ -4196,22 +4295,25 @@
       </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="10">
-        <f>L22+M22+O22+P22</f>
+        <f t="shared" si="2"/>
         <v>18.450000000000003</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S22" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="9">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D23" s="9">
         <v>2</v>
@@ -4223,18 +4325,18 @@
         <v>33</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="I23" s="11"/>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="10">
-        <f>D23*2.2+E23*0.45</f>
+        <f t="shared" si="0"/>
         <v>13.850000000000001</v>
       </c>
       <c r="M23" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F23)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F23)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F23)),-1,0), IF(ISNUMBER(SEARCH("后勤",F23)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N23" s="10">
@@ -4248,22 +4350,22 @@
         <v>4</v>
       </c>
       <c r="Q23" s="10">
-        <f>L23+M23+O23+P23</f>
+        <f t="shared" si="2"/>
         <v>18.200000000000003</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="9">
         <v>2</v>
@@ -4275,45 +4377,45 @@
         <v>33</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
-        <f>D24*2.2+E24*0.45</f>
+        <f t="shared" si="0"/>
         <v>16.100000000000001</v>
       </c>
       <c r="M24" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F24)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F24)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F24)),-1,0), IF(ISNUMBER(SEARCH("后勤",F24)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N24" s="10">
         <v>2</v>
       </c>
       <c r="O24" s="10">
-        <f>N24*2.2</f>
+        <f t="shared" ref="O24:O36" si="3">N24*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P24" s="10"/>
       <c r="Q24" s="10">
-        <f>L24+M24+O24+P24</f>
+        <f t="shared" si="2"/>
         <v>19.5</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="9">
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D25" s="9">
         <v>2</v>
@@ -4325,45 +4427,45 @@
         <v>33</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="10">
-        <f>D25*2.2+E25*0.45</f>
+        <f t="shared" si="0"/>
         <v>13.850000000000001</v>
       </c>
       <c r="M25" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F25)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F25)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F25)),-1,0), IF(ISNUMBER(SEARCH("后勤",F25)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N25" s="10">
         <v>2</v>
       </c>
       <c r="O25" s="10">
-        <f>N25*2.2</f>
+        <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10">
-        <f>L25+M25+O25+P25</f>
+        <f t="shared" si="2"/>
         <v>17.25</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A26" s="9">
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D26" s="9">
         <v>2</v>
@@ -4375,47 +4477,47 @@
         <v>33</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H26" s="9"/>
-      <c r="I26" s="9" t="s">
-        <v>65</v>
+      <c r="I26" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="10">
-        <f>D26*2.2+E26*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.200000000000001</v>
       </c>
       <c r="M26" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F26)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F26)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F26)),-1,0), IF(ISNUMBER(SEARCH("后勤",F26)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="N26" s="10">
         <v>2</v>
       </c>
       <c r="O26" s="10">
-        <f>N26*2.2</f>
+        <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P26" s="10"/>
       <c r="Q26" s="10">
-        <f>L26+M26+O26+P26</f>
+        <f t="shared" si="2"/>
         <v>18.600000000000001</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A27" s="9">
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D27" s="9">
         <v>2</v>
@@ -4424,48 +4526,48 @@
         <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="10">
-        <f>D27*2.2+E27*0.45</f>
+        <f t="shared" si="0"/>
         <v>16.100000000000001</v>
       </c>
       <c r="M27" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F27)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F27)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F27)),-1,0), IF(ISNUMBER(SEARCH("后勤",F27)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="N27" s="10">
         <v>1</v>
       </c>
       <c r="O27" s="10">
-        <f>N27*2.2</f>
+        <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P27" s="10"/>
       <c r="Q27" s="10">
-        <f>L27+M27+O27+P27</f>
+        <f t="shared" si="2"/>
         <v>18.8</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A28" s="9">
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D28" s="9">
         <v>3</v>
@@ -4474,50 +4576,52 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="11"/>
       <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
       <c r="L28" s="10">
-        <f>D28*2.2+E28*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.600000000000001</v>
       </c>
       <c r="M28" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F28)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F28)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F28)),-1,0), IF(ISNUMBER(SEARCH("后勤",F28)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N28" s="10">
         <v>1.5</v>
       </c>
       <c r="O28" s="10">
-        <f>N28*2.2</f>
+        <f t="shared" si="3"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="P28" s="10"/>
       <c r="Q28" s="10">
-        <f>L28+M28+O28+P28</f>
+        <f t="shared" si="2"/>
         <v>21.900000000000002</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S28" s="27" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="103.5" x14ac:dyDescent="0.2">
       <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D29" s="9">
         <v>3</v>
@@ -4527,47 +4631,50 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="22" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="10">
-        <f>D29*2.2+E29*0.45</f>
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
       <c r="M29" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F29)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F29)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F29)),-1,0), IF(ISNUMBER(SEARCH("后勤",F29)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N29" s="10">
         <v>2</v>
       </c>
       <c r="O29" s="10">
-        <f>N29*2.2</f>
+        <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P29" s="10"/>
       <c r="Q29" s="10">
-        <f>L29+M29+O29+P29</f>
+        <f t="shared" si="2"/>
         <v>19.100000000000001</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S29" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A30" s="9">
         <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D30" s="9">
         <v>3</v>
@@ -4576,48 +4683,48 @@
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="10">
-        <f>D30*2.2+E30*0.45</f>
+        <f t="shared" si="0"/>
         <v>13.8</v>
       </c>
       <c r="M30" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F30)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F30)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F30)),-1,0), IF(ISNUMBER(SEARCH("后勤",F30)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="N30" s="10">
         <v>1.5</v>
       </c>
       <c r="O30" s="10">
-        <f>N30*2.2</f>
+        <f t="shared" si="3"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="P30" s="10"/>
       <c r="Q30" s="10">
-        <f>L30+M30+O30+P30</f>
+        <f t="shared" si="2"/>
         <v>18.600000000000001</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="69" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="69" x14ac:dyDescent="0.2">
       <c r="A31" s="9">
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D31" s="9">
         <v>3</v>
@@ -4627,47 +4734,49 @@
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
-      <c r="K31" s="12"/>
       <c r="L31" s="10">
-        <f>D31*2.2+E31*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.600000000000001</v>
       </c>
       <c r="M31" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F31)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F31)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F31)),-1,0), IF(ISNUMBER(SEARCH("后勤",F31)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N31" s="10">
         <v>2</v>
       </c>
       <c r="O31" s="10">
-        <f>N31*2.2</f>
+        <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P31" s="10"/>
       <c r="Q31" s="10">
-        <f>L31+M31+O31+P31</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="17.25" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S31" s="27" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A32" s="9">
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D32" s="9">
         <v>3</v>
@@ -4676,48 +4785,48 @@
         <v>18</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="10">
-        <f>D32*2.2+E32*0.45</f>
+        <f t="shared" si="0"/>
         <v>14.7</v>
       </c>
       <c r="M32" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F32)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F32)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F32)),-1,0), IF(ISNUMBER(SEARCH("后勤",F32)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N32" s="10">
         <v>1</v>
       </c>
       <c r="O32" s="10">
-        <f>N32*2.2</f>
+        <f t="shared" si="3"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P32" s="10"/>
       <c r="Q32" s="10">
-        <f>L32+M32+O32+P32</f>
+        <f t="shared" si="2"/>
         <v>17.899999999999999</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A33" s="9">
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D33" s="9">
         <v>2</v>
@@ -4727,44 +4836,43 @@
       </c>
       <c r="F33" s="9"/>
       <c r="G33" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
       <c r="L33" s="10">
-        <f>D33*2.2+E33*0.45</f>
+        <f t="shared" si="0"/>
         <v>15.200000000000001</v>
       </c>
       <c r="M33" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F33)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F33)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F33)),-1,0), IF(ISNUMBER(SEARCH("后勤",F33)),1,0))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N33" s="10">
         <v>1.5</v>
       </c>
       <c r="O33" s="10">
-        <f>N33*2.2</f>
+        <f t="shared" si="3"/>
         <v>3.3000000000000003</v>
       </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10">
-        <f>L33+M33+O33+P33</f>
+        <f t="shared" si="2"/>
         <v>18.5</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A34" s="9">
         <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>37</v>
@@ -4779,47 +4887,49 @@
         <v>20</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
       <c r="L34" s="10">
-        <f>D34*2.2+E34*0.45</f>
+        <f t="shared" ref="L34:L51" si="4">D34*2.2+E34*0.45</f>
         <v>10.3</v>
       </c>
       <c r="M34" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
+        <f t="shared" ref="M34:M51" si="5">SUM(IF(ISNUMBER(SEARCH("疾行",F34)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F34)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F34)),-1,0), IF(ISNUMBER(SEARCH("后勤",F34)),1,0))</f>
         <v>0</v>
       </c>
       <c r="N34" s="10">
         <v>2.5</v>
       </c>
       <c r="O34" s="10">
-        <f>N34*2.2</f>
+        <f t="shared" si="3"/>
         <v>5.5</v>
       </c>
       <c r="P34" s="10"/>
       <c r="Q34" s="10">
-        <f>L34+M34+O34+P34</f>
+        <f t="shared" ref="Q34:Q50" si="6">L34+M34+O34+P34</f>
         <v>15.8</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="57" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S34" s="27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A35" s="9">
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D35" s="9">
         <v>3</v>
@@ -4828,52 +4938,53 @@
         <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="10">
-        <f>D35*2.2+E35*0.45</f>
+        <f t="shared" si="4"/>
         <v>13.350000000000001</v>
       </c>
       <c r="M35" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F35)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F35)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F35)),-1,0), IF(ISNUMBER(SEARCH("后勤",F35)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="N35" s="10">
         <v>3</v>
       </c>
       <c r="O35" s="10">
-        <f>N35*2.2</f>
+        <f t="shared" si="3"/>
         <v>6.6000000000000005</v>
       </c>
       <c r="P35" s="10"/>
       <c r="Q35" s="10">
-        <f>L35+M35+O35+P35</f>
+        <f t="shared" si="6"/>
         <v>21.450000000000003</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S35" s="9"/>
+    </row>
+    <row r="36" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A36" s="9">
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D36" s="9">
         <v>3</v>
@@ -4885,47 +4996,50 @@
         <v>20</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
       <c r="L36" s="10">
-        <f>D36*2.2+E36*0.45</f>
+        <f t="shared" si="4"/>
         <v>15.600000000000001</v>
       </c>
       <c r="M36" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F36)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F36)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F36)),-1,0), IF(ISNUMBER(SEARCH("后勤",F36)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N36" s="10">
         <v>2</v>
       </c>
       <c r="O36" s="10">
-        <f>N36*2.2</f>
+        <f t="shared" si="3"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P36" s="10"/>
       <c r="Q36" s="10">
-        <f>L36+M36+O36+P36</f>
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S36" s="9" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A37" s="9">
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D37" s="9">
         <v>2</v>
@@ -4934,21 +5048,21 @@
         <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="10">
-        <f>D37*2.2+E37*0.45</f>
+        <f t="shared" si="4"/>
         <v>13.4</v>
       </c>
       <c r="M37" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F37)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F37)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F37)),-1,0), IF(ISNUMBER(SEARCH("后勤",F37)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="N37" s="10">
@@ -4960,22 +5074,22 @@
       </c>
       <c r="P37" s="10"/>
       <c r="Q37" s="10">
-        <f>L37+M37+O37+P37</f>
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
       <c r="R37" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A38" s="9">
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D38" s="9">
         <v>2</v>
@@ -4985,47 +5099,50 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="21" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="10">
-        <f>D38*2.2+E38*0.45</f>
+        <f t="shared" si="4"/>
         <v>13.4</v>
       </c>
       <c r="M38" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F38)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F38)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F38)),-1,0), IF(ISNUMBER(SEARCH("后勤",F38)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N38" s="10">
         <v>2</v>
       </c>
       <c r="O38" s="10">
-        <f>N38*2.2</f>
+        <f t="shared" ref="O38:O43" si="7">N38*2.2</f>
         <v>4.4000000000000004</v>
       </c>
       <c r="P38" s="10"/>
       <c r="Q38" s="10">
-        <f>L38+M38+O38+P38</f>
+        <f t="shared" si="6"/>
         <v>17.8</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="S38" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A39" s="9">
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D39" s="9">
         <v>0</v>
@@ -5034,48 +5151,48 @@
         <v>27</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="10">
-        <f>D39*2.2+E39*0.45</f>
+        <f t="shared" si="4"/>
         <v>12.15</v>
       </c>
       <c r="M39" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F39)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F39)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F39)),-1,0), IF(ISNUMBER(SEARCH("后勤",F39)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="N39" s="10">
         <v>2</v>
       </c>
       <c r="O39" s="10">
-        <f>N39*2.2</f>
+        <f t="shared" si="7"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P39" s="10"/>
       <c r="Q39" s="10">
-        <f>L39+M39+O39+P39</f>
+        <f t="shared" si="6"/>
         <v>17.55</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A40" s="9">
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D40" s="9">
         <v>3</v>
@@ -5087,45 +5204,45 @@
         <v>45</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="10">
-        <f>D40*2.2+E40*0.45</f>
+        <f t="shared" si="4"/>
         <v>14.25</v>
       </c>
       <c r="M40" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F40)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F40)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F40)),-1,0), IF(ISNUMBER(SEARCH("后勤",F40)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N40" s="10">
         <v>2</v>
       </c>
       <c r="O40" s="10">
-        <f>N40*2.2</f>
+        <f t="shared" si="7"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P40" s="10"/>
       <c r="Q40" s="10">
-        <f>L40+M40+O40+P40</f>
+        <f t="shared" si="6"/>
         <v>18.649999999999999</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D41" s="9">
         <v>5</v>
@@ -5135,45 +5252,45 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="10">
-        <f>D41*2.2+E41*0.45</f>
+        <f t="shared" si="4"/>
         <v>16.850000000000001</v>
       </c>
       <c r="M41" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F41)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F41)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F41)),-1,0), IF(ISNUMBER(SEARCH("后勤",F41)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N41" s="10">
         <v>2</v>
       </c>
       <c r="O41" s="10">
-        <f>N41*2.2</f>
+        <f t="shared" si="7"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="P41" s="10"/>
       <c r="Q41" s="10">
-        <f>L41+M41+O41+P41</f>
+        <f t="shared" si="6"/>
         <v>21.25</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A42" s="9">
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D42" s="9">
         <v>2</v>
@@ -5183,47 +5300,49 @@
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="21" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
       <c r="L42" s="10">
-        <f>D42*2.2+E42*0.45</f>
+        <f t="shared" si="4"/>
         <v>15.200000000000001</v>
       </c>
       <c r="M42" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F42)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F42)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F42)),-1,0), IF(ISNUMBER(SEARCH("后勤",F42)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N42" s="10">
         <v>1</v>
       </c>
       <c r="O42" s="10">
-        <f>N42*2.2</f>
+        <f t="shared" si="7"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="P42" s="10"/>
       <c r="Q42" s="10">
-        <f>L42+M42+O42+P42</f>
+        <f t="shared" si="6"/>
         <v>17.400000000000002</v>
       </c>
       <c r="R42" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="51.75" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="S42" s="27" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
       <c r="A43" s="9">
         <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D43" s="9">
         <v>2</v>
@@ -5235,45 +5354,45 @@
         <v>14</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
       <c r="L43" s="10">
-        <f>D43*2.2+E43*0.45</f>
+        <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
       <c r="M43" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F43)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F43)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F43)),-1,0), IF(ISNUMBER(SEARCH("后勤",F43)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="N43" s="10">
         <v>3</v>
       </c>
       <c r="O43" s="10">
-        <f>N43*2.2</f>
+        <f t="shared" si="7"/>
         <v>6.6000000000000005</v>
       </c>
       <c r="P43" s="10"/>
       <c r="Q43" s="10">
-        <f>L43+M43+O43+P43</f>
+        <f t="shared" si="6"/>
         <v>20.6</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="30" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>43</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D44" s="9">
         <v>1</v>
@@ -5285,18 +5404,18 @@
         <v>20</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
       <c r="L44" s="10">
-        <f>D44*2.2+E44*0.45</f>
+        <f t="shared" si="4"/>
         <v>8.5</v>
       </c>
       <c r="M44" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F44)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F44)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F44)),-1,0), IF(ISNUMBER(SEARCH("后勤",F44)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N44" s="10">
@@ -5310,22 +5429,22 @@
         <v>4</v>
       </c>
       <c r="Q44" s="10">
-        <f>L44+M44+O44+P44</f>
+        <f t="shared" si="6"/>
         <v>15.2</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="45" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="45" x14ac:dyDescent="0.2">
       <c r="A45" s="9">
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D45" s="9">
         <v>2</v>
@@ -5337,20 +5456,20 @@
         <v>33</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H45" s="9"/>
-      <c r="I45" s="9" t="s">
-        <v>95</v>
+      <c r="I45" s="28" t="s">
+        <v>231</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
       <c r="L45" s="10">
-        <f>D45*2.2+E45*0.45</f>
+        <f t="shared" si="4"/>
         <v>16.100000000000001</v>
       </c>
       <c r="M45" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F45)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F45)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F45)),-1,0), IF(ISNUMBER(SEARCH("后勤",F45)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="N45" s="10">
@@ -5362,22 +5481,22 @@
       </c>
       <c r="P45" s="10"/>
       <c r="Q45" s="10">
-        <f>L45+M45+O45+P45</f>
+        <f t="shared" si="6"/>
         <v>19.5</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="60" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="9">
         <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D46" s="9">
         <v>3</v>
@@ -5389,18 +5508,18 @@
         <v>20</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
       <c r="L46" s="10">
-        <f>D46*2.2+E46*0.45</f>
+        <f t="shared" si="4"/>
         <v>13.8</v>
       </c>
       <c r="M46" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F46)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F46)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F46)),-1,0), IF(ISNUMBER(SEARCH("后勤",F46)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N46" s="10">
@@ -5412,22 +5531,22 @@
       </c>
       <c r="P46" s="10"/>
       <c r="Q46" s="10">
-        <f>L46+M46+O46+P46</f>
+        <f t="shared" si="6"/>
         <v>18.200000000000003</v>
       </c>
       <c r="R46" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="34.5" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A47" s="9">
         <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -5436,23 +5555,23 @@
         <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H47" s="9"/>
-      <c r="I47" s="11" t="s">
-        <v>218</v>
+      <c r="I47" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
       <c r="L47" s="10">
-        <f>D47*2.2+E47*0.45</f>
+        <f t="shared" si="4"/>
         <v>12.950000000000001</v>
       </c>
       <c r="M47" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F47)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F47)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F47)),-1,0), IF(ISNUMBER(SEARCH("后勤",F47)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="N47" s="10">
@@ -5464,22 +5583,22 @@
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="10">
-        <f>L47+M47+O47+P47</f>
+        <f t="shared" si="6"/>
         <v>18.850000000000001</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
       <c r="A48" s="9">
         <v>47</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D48" s="9">
         <v>0</v>
@@ -5491,20 +5610,20 @@
         <v>14</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
       <c r="K48" s="9"/>
       <c r="L48" s="10">
-        <f>D48*2.2+E48*0.45</f>
+        <f t="shared" si="4"/>
         <v>8.1</v>
       </c>
       <c r="M48" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F48)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F48)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F48)),-1,0), IF(ISNUMBER(SEARCH("后勤",F48)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="N48" s="10">
@@ -5516,11 +5635,14 @@
       </c>
       <c r="P48" s="10"/>
       <c r="Q48" s="10">
-        <f>L48+M48+O48+P48</f>
+        <f t="shared" si="6"/>
         <v>18.399999999999999</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
+      </c>
+      <c r="S48" s="12" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -5528,10 +5650,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -5543,18 +5665,18 @@
         <v>33</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
       <c r="K49" s="9"/>
       <c r="L49" s="10">
-        <f>D49*2.2+E49*0.45</f>
+        <f t="shared" si="4"/>
         <v>18.399999999999999</v>
       </c>
       <c r="M49" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F49)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F49)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F49)),-1,0), IF(ISNUMBER(SEARCH("后勤",F49)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="N49" s="10">
@@ -5566,22 +5688,22 @@
       </c>
       <c r="P49" s="10"/>
       <c r="Q49" s="10">
-        <f>L49+M49+O49+P49</f>
+        <f t="shared" si="6"/>
         <v>18.75</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D50" s="4">
         <v>2</v>
@@ -5593,20 +5715,20 @@
         <v>33</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H50" s="4"/>
-      <c r="I50" s="34" t="s">
-        <v>219</v>
+      <c r="I50" s="28" t="s">
+        <v>232</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="10">
-        <f>D50*2.2+E50*0.45</f>
+        <f t="shared" si="4"/>
         <v>14.3</v>
       </c>
       <c r="M50" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F50)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F50)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F50)),-1,0), IF(ISNUMBER(SEARCH("后勤",F50)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="N50" s="10"/>
@@ -5618,22 +5740,22 @@
         <v>4</v>
       </c>
       <c r="Q50" s="10">
-        <f>L50+M50+O50+P50</f>
+        <f t="shared" si="6"/>
         <v>17.3</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
@@ -5643,18 +5765,18 @@
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="10">
-        <f>D51*2.2+E51*0.45</f>
+        <f t="shared" si="4"/>
         <v>2.6500000000000004</v>
       </c>
       <c r="M51" s="10">
-        <f>SUM(IF(ISNUMBER(SEARCH("疾行",F51)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F51)),1.5,0), IF(ISNUMBER(SEARCH("嘲讽",F51)),-1,0), IF(ISNUMBER(SEARCH("后勤",F51)),1,0))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="N51" s="10"/>
@@ -5695,42 +5817,1302 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBE2D7C-DF0B-49B4-9FE7-BB09A920D14C}">
+  <dimension ref="A1:S17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="S1" s="27" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>50</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兽族</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狗头军师</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>22</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我方回合中，站在狗头军师相邻的队友攻击力+1。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需要攻击力加成的角色</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白游侠、烛火、长剑、末日</t>
+        </is>
+      </c>
+      <c r="L2">
+        <v>14.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>4.4</v>
+      </c>
+      <c r="Q2">
+        <v>18.7</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">嬉皮死神×2、小阴影、长角、共鸣者</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>51</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兽族</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狂徒</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>13</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最好搭配一个坦克</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
+        </is>
+      </c>
+      <c r="L3">
+        <v>19.05</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>19.05</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白板</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔盾、圣光、复仇者</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>52</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兽族</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拾荒者</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;疾行&gt;</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拾取增益道具或金矿时，额外永久获得1点攻击力（最多+3）。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能产生道具或金矿的角色</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、暗域、宿魂</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圣诞老人、黄金矿工</t>
+        </is>
+      </c>
+      <c r="L4">
+        <v>13.4</v>
+      </c>
+      <c r="M4">
+        <v>1.5</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4">
+        <v>4.4</v>
+      </c>
+      <c r="Q4">
+        <v>19.3</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输出</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圣诞老人、黄金矿工、风语者</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>53</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兽族</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">图腾师</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>32</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">己方回合开始时，在相邻空地立一根图腾（耐久3，同时最多2根）。与图腾相邻的己方单位受到攻击伤害-1。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需要保护的远程角色</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">伐木工、烛火、末日、白游侠</t>
+        </is>
+      </c>
+      <c r="L5">
+        <v>16.6</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>4</v>
+      </c>
+      <c r="O5">
+        <v>1.8</v>
+      </c>
+      <c r="Q5">
+        <v>18.4</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉盾</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、医护兵</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>54</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">兽族</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">血牙斗士</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;嘲讽&gt;</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每受到一次伤害，攻击力+1，直到我方回合结束。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能治疗自己的角色</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鼠队长、白游侠、死灵法师</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赏金猎人、影丸、红帽</t>
+        </is>
+      </c>
+      <c r="L6">
+        <v>15.2</v>
+      </c>
+      <c r="M6">
+        <v>-1</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>4.4</v>
+      </c>
+      <c r="Q6">
+        <v>18.6</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉盾</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医护兵、德鲁伊、圣光</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>55</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">拆弹手</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>19</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移动后，拆除相邻格上的敌方炸弹，每拆除一颗回复4点HP；不会受到炸弹伤害。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需要贴身保护的角色</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">炸弹人</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、鼠队长</t>
+        </is>
+      </c>
+      <c r="L7">
+        <v>15.15</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1.5</v>
+      </c>
+      <c r="O7">
+        <v>3.3</v>
+      </c>
+      <c r="Q7">
+        <v>18.45</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔盾、独脚龟</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>56</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破盾锤</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻击无视目标的[圣盾]；若目标带有[圣盾]，本次伤害翻倍。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能提供攻击力加成的角色</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">波盾、圣光</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔盾、独脚龟、装甲堡垒</t>
+        </is>
+      </c>
+      <c r="L8">
+        <v>15.6</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>2</v>
+      </c>
+      <c r="O8">
+        <v>4.4</v>
+      </c>
+      <c r="Q8">
+        <v>20</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输出</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">烈焰祭司、圣诞老人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>57</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">铆钉机兵</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>31</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;嘲讽&gt;</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到近战攻击时，对攻击者造成2点伤害。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能提供圣盾或治疗的角色</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鼠队长、太阳斩、嬉皮死神</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
+        </is>
+      </c>
+      <c r="L9">
+        <v>16.15</v>
+      </c>
+      <c r="M9">
+        <v>-1</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <v>4.4</v>
+      </c>
+      <c r="Q9">
+        <v>19.55</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉盾</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">圣光、荆棘树人</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>58</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">绊线工兵</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>17</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移动后，可在相邻空格布设一条绊线；敌人经过或停留时触发，获得[眩晕]，触发后消失。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能使敌人位移的角色</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坠炮手、宿魂、影丸</t>
+        </is>
+      </c>
+      <c r="L10">
+        <v>14.25</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+      <c r="O10">
+        <v>4.4</v>
+      </c>
+      <c r="Q10">
+        <v>18.65</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傀儡师、超新星、长角、血锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>59</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机械</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">哨戒机</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>22</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">最好搭配一个坦克</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暗域、宿魂、影丸</t>
+        </is>
+      </c>
+      <c r="L11">
+        <v>18.7</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>18.7</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白板</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔盾、独脚龟</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>60</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精灵</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">净化祭司</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>18</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">己方回合开始时，清除所有队友身上的负面状态；每清除一个，本回合自身攻击力+1（最多+3）。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">需要站在前排的角色</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">战锤、雪拳、巨剑、沉默术士、荆棘树人、宿魂、猎颅者、白游侠</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、毒蛇淑女</t>
+        </is>
+      </c>
+      <c r="L12">
+        <v>12.5</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12">
+        <v>6.6</v>
+      </c>
+      <c r="Q12">
+        <v>19.1</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">塔盾、装甲堡垒、独脚龟</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>61</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精灵</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">卸力僧</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻击后，令目标本回合无法反击。自身反击时造成2倍伤害。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能提供攻击力加成的角色</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">复仇者、塔盾、装甲堡垒、荆棘树人、战锤、负墟</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
+        </is>
+      </c>
+      <c r="L13">
+        <v>14.3</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>2</v>
+      </c>
+      <c r="O13">
+        <v>4.4</v>
+      </c>
+      <c r="Q13">
+        <v>18.7</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">肉盾</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">医护兵、德鲁伊、风语者</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>62</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">精灵</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">霜语者</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>26</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">己方回合开始时，令所有敌人获得[冰冻]，对方回合结束时解除。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">近战角色</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">风语者、影丸、鼠队长</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">负墟</t>
+        </is>
+      </c>
+      <c r="L14">
+        <v>13.9</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>2</v>
+      </c>
+      <c r="O14">
+        <v>4.4</v>
+      </c>
+      <c r="Q14">
+        <v>18.3</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">长剑、暗域、大骑士</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>63</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">魔族</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">掘墓人</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15">
+        <v>20</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">移动后，摧毁相邻的敌方墓碑（该格不能再被替补落位）；若相邻的是己方墓碑，改为回复6点HP。</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能提供攻击力加成的角色</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">波盾、太阳斩、猎颅者、梅林</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、火枪手、鼠队长</t>
+        </is>
+      </c>
+      <c r="L15">
+        <v>15.6</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>1.5</v>
+      </c>
+      <c r="O15">
+        <v>3.3</v>
+      </c>
+      <c r="Q15">
+        <v>18.9</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">红帽、嬉皮死神、暗域</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>64</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">魔族</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瘟疫使者</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>21</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻击后，令目标无法回复HP，直到对方回合结束；若目标已带有任意负面状态，额外造成3点无视圣盾的伤害。</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">能施加负面状态的角色</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">德鲁伊、医护兵、梅林、古拉博士、塔盾、复仇者、风语者</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">负墟、圣光</t>
+        </is>
+      </c>
+      <c r="L16">
+        <v>13.85</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>4.4</v>
+      </c>
+      <c r="Q16">
+        <v>18.25</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">输出</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毒蛇淑女、战锤、雪拳、巨剑、荆棘树人、沉默术士</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>65</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人族</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">号令官</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;远程&gt;</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">我方回合开始时，令相邻队友本回合首次攻击的伤害+2。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高攻击力或高倍率的角色</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白游侠、烛火、末日</t>
+        </is>
+      </c>
+      <c r="L17">
+        <v>15.2</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>1.5</v>
+      </c>
+      <c r="O17">
+        <v>3.3</v>
+      </c>
+      <c r="Q17">
+        <v>18.5</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辅助</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">影丸、红帽、鼠队长、小阴影</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7102D913-C566-45C6-A81B-A23758E65E8F}">
+  <dimension ref="A5:B17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="34"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B7" s="3">
+        <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="3">
+        <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="3">
+        <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" s="3">
+        <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="3">
+        <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="3">
+        <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="3">
+        <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="3">
+        <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B17" s="3">
+        <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:B5"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A54A7-3772-444D-AA2D-5E70DBC959BF}">
   <dimension ref="A4:Q26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
+      <c r="A4" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
+      <c r="A5" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -5750,10 +7132,10 @@
     </row>
     <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -5762,10 +7144,10 @@
     </row>
     <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -5785,10 +7167,10 @@
     </row>
     <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -5808,10 +7190,10 @@
     </row>
     <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -5831,10 +7213,10 @@
     </row>
     <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -5854,10 +7236,10 @@
     </row>
     <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -5877,21 +7259,21 @@
     </row>
     <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="A14" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
     </row>
     <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -5911,10 +7293,10 @@
     </row>
     <row r="16" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -5934,10 +7316,10 @@
     </row>
     <row r="17" spans="1:17" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5957,10 +7339,10 @@
     </row>
     <row r="18" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -5980,10 +7362,10 @@
     </row>
     <row r="19" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -6003,10 +7385,10 @@
     </row>
     <row r="20" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -6026,10 +7408,10 @@
     </row>
     <row r="21" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -6049,10 +7431,10 @@
     </row>
     <row r="22" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -6072,10 +7454,10 @@
     </row>
     <row r="23" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -6095,10 +7477,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -6118,10 +7500,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -6140,14 +7522,14 @@
       <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
+      <c r="A26" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6161,127 +7543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7102D913-C566-45C6-A81B-A23758E65E8F}">
-  <dimension ref="A5:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="32"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="3">
-        <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="B8" s="3">
-        <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="B9" s="3">
-        <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="B10" s="3">
-        <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="B11" s="3">
-        <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="B14" s="3">
-        <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="B15" s="3">
-        <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B16" s="3">
-        <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B17" s="3">
-        <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:B5"/>
-  </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CF6EE44-8C24-409F-B95B-366E700D4059}">
   <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6291,47 +7553,47 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+        <v>104</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
-      <c r="G12" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
+      <c r="G12" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -6347,7 +7609,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -6366,7 +7628,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -6385,7 +7647,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -6404,7 +7666,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -6423,7 +7685,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H18">
         <v>1</v>

--- a/Data/Hero/角色列表.xlsx
+++ b/Data/Hero/角色列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\Data\Hero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7DD762E-1906-4E4E-BCE0-303B4B401295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CB8C1D-50C9-4258-9750-3837CC9E2A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="4650" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60" yWindow="3705" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">角色列表!$A$1:$R$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="448">
   <si>
     <t>No.</t>
   </si>
@@ -2446,10 +2447,6 @@
     <t>嬉皮死神×3、炸弹人×3、烛火×3</t>
   </si>
   <si>
-    <t>嬉皮死神×3、烛火×1、炸弹人×3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>长剑</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2462,14 +2459,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>嬉皮死神×3、烛火×1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>毒蛇淑女、白游侠、小阴影、烛火、长剑、赏金猎人、圣光、复仇者、暗域、嬉皮死神、长角、沉默术士、黄金矿工、风语者、宿魂、共鸣者、荆棘树人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>傀儡师×3、超新星×3、暗域×3、长角、血锁×3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2488,23 +2477,662 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>毒蛇淑女、烛火、圣光、复仇者、暗域、古灵精怪、嬉皮死神、涌电技师、红帽、宿魂、共鸣者、荆棘树人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>影丸、烈焰祭司、沉默术士、风语者、坠炮手、涌电技师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鼠队长、影丸、火枪手、古拉博士、红帽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>狗头军师</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我方回合中，站在狗头军师附近的队友</t>
+    <t>兽族</t>
+  </si>
+  <si>
+    <t>辅助</t>
+  </si>
+  <si>
+    <t>狂徒</t>
+  </si>
+  <si>
+    <t>影丸、火枪手、坠炮手</t>
+  </si>
+  <si>
+    <t>白板</t>
+  </si>
+  <si>
+    <t>塔盾、圣光、复仇者</t>
+  </si>
+  <si>
+    <t>输出</t>
+  </si>
+  <si>
+    <t>肉盾</t>
+  </si>
+  <si>
+    <t>能治疗自己的角色</t>
+  </si>
+  <si>
+    <t>鼠队长、白游侠、死灵法师</t>
+  </si>
+  <si>
+    <t>赏金猎人、影丸、红帽</t>
+  </si>
+  <si>
+    <t>医护兵、德鲁伊、圣光</t>
+  </si>
+  <si>
+    <t>机械</t>
+  </si>
+  <si>
+    <t>塔盾、独脚龟</t>
+  </si>
+  <si>
+    <t>破盾锤</t>
+  </si>
+  <si>
+    <t>攻击无视目标的[圣盾]；若目标带有[圣盾]，本次伤害翻倍。</t>
+  </si>
+  <si>
+    <t>波盾、圣光</t>
+  </si>
+  <si>
+    <t>塔盾、独脚龟、装甲堡垒</t>
+  </si>
+  <si>
+    <t>烈焰祭司、圣诞老人</t>
+  </si>
+  <si>
+    <t>受到近战攻击时，对攻击者造成2点伤害。</t>
+  </si>
+  <si>
+    <t>能提供圣盾或治疗的角色</t>
+  </si>
+  <si>
+    <t>鼠队长、太阳斩、嬉皮死神</t>
+  </si>
+  <si>
+    <t>圣光、荆棘树人</t>
+  </si>
+  <si>
+    <t>哨戒机</t>
+  </si>
+  <si>
+    <t>暗域、宿魂、影丸</t>
+  </si>
+  <si>
+    <t>精灵</t>
+  </si>
+  <si>
+    <t>净化祭司</t>
+  </si>
+  <si>
+    <t>己方回合开始时，清除所有队友身上的负面状态；每清除一个，本回合自身攻击力+1（最多+3）。</t>
+  </si>
+  <si>
+    <t>需要站在前排的角色</t>
+  </si>
+  <si>
+    <t>战锤、雪拳、巨剑、沉默术士、荆棘树人、宿魂、猎颅者、白游侠</t>
+  </si>
+  <si>
+    <t>影丸、火枪手、毒蛇淑女</t>
+  </si>
+  <si>
+    <t>塔盾、装甲堡垒、独脚龟</t>
+  </si>
+  <si>
+    <t>卸力僧</t>
+  </si>
+  <si>
+    <t>攻击后，令目标本回合无法反击。自身反击时造成2倍伤害。</t>
+  </si>
+  <si>
+    <t>复仇者、塔盾、装甲堡垒、荆棘树人、战锤、负墟</t>
+  </si>
+  <si>
+    <t>医护兵、德鲁伊、风语者</t>
+  </si>
+  <si>
+    <t>霜语者</t>
+  </si>
+  <si>
+    <t>己方回合开始时，令所有敌人获得[冰冻]，对方回合结束时解除。</t>
+  </si>
+  <si>
+    <t>近战角色</t>
+  </si>
+  <si>
+    <t>风语者、影丸、鼠队长</t>
+  </si>
+  <si>
+    <t>长剑、暗域、大骑士</t>
+  </si>
+  <si>
+    <t>魔族</t>
+  </si>
+  <si>
+    <t>瘟疫使者</t>
+  </si>
+  <si>
+    <t>能施加负面状态的角色</t>
+  </si>
+  <si>
+    <t>德鲁伊、医护兵、梅林、古拉博士、塔盾、复仇者、风语者</t>
+  </si>
+  <si>
+    <t>负墟、圣光</t>
+  </si>
+  <si>
+    <t>毒蛇淑女、战锤、雪拳、巨剑、荆棘树人、沉默术士</t>
+  </si>
+  <si>
+    <t>人族</t>
+  </si>
+  <si>
+    <t>禁反击</t>
+  </si>
+  <si>
+    <t>狼骑士</t>
+  </si>
+  <si>
+    <t>风语者、大骑士</t>
+  </si>
+  <si>
+    <t>蛮牛卫士</t>
+  </si>
+  <si>
+    <t>回合结束时，若本回合没有移动，回复5点HP。</t>
+  </si>
+  <si>
+    <t>能治疗或提供圣盾的角色</t>
+  </si>
+  <si>
+    <t>赏金猎人、沉默术士、影丸</t>
+  </si>
+  <si>
+    <t>装甲堡垒、独脚龟</t>
+  </si>
+  <si>
+    <t>毒牙猎手</t>
+  </si>
+  <si>
+    <t>沉默术士、猎颅者</t>
+  </si>
+  <si>
+    <t>影丸、红帽、鼠队长</t>
+  </si>
+  <si>
+    <t>碎骨者</t>
+  </si>
+  <si>
+    <t>能站在前排的角色</t>
+  </si>
+  <si>
+    <t>沉默术士、影丸、火枪手</t>
+  </si>
+  <si>
+    <t>塔盾、装甲堡垒</t>
+  </si>
+  <si>
+    <t>能造成高额伤害的角色</t>
+  </si>
+  <si>
+    <t>山猪撞角</t>
+  </si>
+  <si>
+    <t>超新星、长角、血锁</t>
+  </si>
+  <si>
+    <t>赏金猎人、影丸、火枪手</t>
+  </si>
+  <si>
+    <t>铆钉炮台</t>
+  </si>
+  <si>
+    <t>己方回合结束时，对最近的敌人造成3点伤害。</t>
+  </si>
+  <si>
+    <t>能保护它的角色</t>
+  </si>
+  <si>
+    <t>影丸、火枪手、暗域</t>
+  </si>
+  <si>
+    <t>塔盾、独脚龟、荆棘树人</t>
+  </si>
+  <si>
+    <t>影丸、火枪手、傀儡师</t>
+  </si>
+  <si>
+    <t>梅林、医护兵、德鲁伊</t>
+  </si>
+  <si>
+    <t>铁盾卫士</t>
+  </si>
+  <si>
+    <t>相邻的队友受到的远程伤害-1。</t>
+  </si>
+  <si>
+    <t>需要贴身保护的远程角色</t>
+  </si>
+  <si>
+    <t>白游侠、影丸、火枪手</t>
+  </si>
+  <si>
+    <t>赏金猎人、烛火、末日</t>
+  </si>
+  <si>
+    <t>塔盾、独脚龟、医护兵</t>
+  </si>
+  <si>
+    <t>能提供移动力的角色</t>
+  </si>
+  <si>
+    <t>攻击后，对目标相邻的另一个敌人造成2点伤害。</t>
+  </si>
+  <si>
+    <t>能使敌人聚拢的角色</t>
+  </si>
+  <si>
+    <t>傀儡师、血锁、长角</t>
+  </si>
+  <si>
+    <t>负墟、影丸、火枪手</t>
+  </si>
+  <si>
+    <t>需要保护的队友</t>
+  </si>
+  <si>
+    <t>能压低敌人HP的角色</t>
+  </si>
+  <si>
+    <t>影丸、小阴影、赏金猎人</t>
+  </si>
+  <si>
+    <t>医护兵、德鲁伊、古拉博士</t>
+  </si>
+  <si>
+    <t>魅影刺客</t>
+  </si>
+  <si>
+    <t>塔盾、圣光、暗域</t>
+  </si>
+  <si>
+    <t>能把它送进人堆的角色</t>
+  </si>
+  <si>
+    <t>沉默术士、猎颅者、坠炮手</t>
+  </si>
+  <si>
+    <t>暗域、宿魂、大骑士</t>
+  </si>
+  <si>
+    <t>噬魂者</t>
+  </si>
+  <si>
+    <t>攻击后，若目标在本回合内死亡，回复8点HP。</t>
+  </si>
+  <si>
+    <t>军旗手</t>
+  </si>
+  <si>
+    <t>阵亡时，令所有队友永久获得攻击力+1。</t>
+  </si>
+  <si>
+    <t>沉默术士、猎颅者、赏金猎人</t>
+  </si>
+  <si>
+    <t>影丸、红帽、共鸣者</t>
+  </si>
+  <si>
+    <t>重装步兵</t>
+  </si>
+  <si>
+    <t>受到的伤害小于3时，改为0。</t>
+  </si>
+  <si>
+    <t>影丸、红帽、古拉博士</t>
+  </si>
+  <si>
+    <t>神射手</t>
+  </si>
+  <si>
+    <t>若本回合没有移动，攻击力+2。</t>
+  </si>
+  <si>
+    <t>站桩才有输出</t>
+  </si>
+  <si>
+    <t>蓄能兵</t>
+  </si>
+  <si>
+    <t>若本回合没有攻击，则下回合攻击力+2（可累计，最多+4；攻击后清零）。</t>
+  </si>
+  <si>
+    <t>蓄力-爆发节奏</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>攻击力额外+（已损失HP ÷ 4）。</t>
+  </si>
+  <si>
+    <t>血越少越猛</t>
+  </si>
+  <si>
+    <t>苦修者</t>
+  </si>
+  <si>
+    <t>攻击后，自身受到2点伤害。</t>
+  </si>
+  <si>
+    <t>自伤换伤害</t>
+  </si>
+  <si>
+    <t>老兵</t>
+  </si>
+  <si>
+    <t>每经过一个完整回合，永久攻击力+1（最多+3）。</t>
+  </si>
+  <si>
+    <t>塔盾、圣光、独脚龟</t>
+  </si>
+  <si>
+    <t>越拖越强</t>
+  </si>
+  <si>
+    <t>击杀即续航</t>
+  </si>
+  <si>
+    <t>食尸鬼</t>
+  </si>
+  <si>
+    <t>击杀敌人后，永久攻击力+1（最多+3）。</t>
+  </si>
+  <si>
+    <t>抢人头滚雪球</t>
+  </si>
+  <si>
+    <t>专破圣盾</t>
+  </si>
+  <si>
+    <t>星火法师</t>
+  </si>
+  <si>
+    <t>溅射逼走位</t>
+  </si>
+  <si>
+    <t>攻击时，若目标带有任意负面状态，伤害+2。</t>
+  </si>
+  <si>
+    <t>毒蛇淑女、战锤、雪拳、巨剑、荆棘树人</t>
+  </si>
+  <si>
+    <t>专打带状态的敌人</t>
+  </si>
+  <si>
+    <t>若本回合移动了3格或更多，本次攻击伤害+2。</t>
+  </si>
+  <si>
+    <t>长距离冲刺</t>
+  </si>
+  <si>
+    <t>猩红骑士</t>
+  </si>
+  <si>
+    <t>移动后，回复等同于本次移动距离的HP。</t>
+  </si>
+  <si>
+    <t>风语者、大骑士、宿魂</t>
+  </si>
+  <si>
+    <t>打带跑续航</t>
+  </si>
+  <si>
+    <t>掠夺者</t>
+  </si>
+  <si>
+    <t>攻击后，偷取目标1点攻击力（永久，最多+3）。</t>
+  </si>
+  <si>
+    <t>塔盾、装甲堡垒、古拉博士</t>
+  </si>
+  <si>
+    <t>塔盾、独脚龟、圣光</t>
+  </si>
+  <si>
+    <t>专偷高攻单位</t>
+  </si>
+  <si>
+    <t>推着走的炮台</t>
+  </si>
+  <si>
+    <t>攻击后，将目标击退1格；若目标撞上其他单位，双方各受2点伤害。</t>
+  </si>
+  <si>
+    <t>撞人连锁伤</t>
+  </si>
+  <si>
+    <t>自爆机兵</t>
+  </si>
+  <si>
+    <t>阵亡时，对相邻的所有敌人造成6点伤害。</t>
+  </si>
+  <si>
+    <t>死亡威慑</t>
+  </si>
+  <si>
+    <t>磁石兵</t>
+  </si>
+  <si>
+    <t>己方回合开始时，将相邻的所有敌人拉近1格。</t>
+  </si>
+  <si>
+    <t>能承受集火的角色</t>
+  </si>
+  <si>
+    <t>烛火、末日、白游侠</t>
+  </si>
+  <si>
+    <t>把敌人拽过来</t>
+  </si>
+  <si>
+    <t>潮汐师</t>
+  </si>
+  <si>
+    <t>攻击后，将目标推开1格，然后自己移动到目标原来的位置。</t>
+  </si>
+  <si>
+    <t>复仇者、荆棘树人</t>
+  </si>
+  <si>
+    <t>推开并抢占位置</t>
+  </si>
+  <si>
+    <t>换位僧</t>
+  </si>
+  <si>
+    <t>移动后，可与相邻的任意单位（含敌人）交换位置。</t>
+  </si>
+  <si>
+    <t>把谁放到哪</t>
+  </si>
+  <si>
+    <t>全场减速</t>
+  </si>
+  <si>
+    <t>干扰者</t>
+  </si>
+  <si>
+    <t>相邻的敌人无法使用技能。</t>
+  </si>
+  <si>
+    <t>烛火、圣光、复仇者、暗域、古灵精怪、嬉皮死神、涌电技师、红帽、宿魂、共鸣者、荆棘树人、沉默术士</t>
+  </si>
+  <si>
+    <t>贴脸封技能</t>
+  </si>
+  <si>
+    <t>伪旗手</t>
+  </si>
+  <si>
+    <t>己方回合开始时，令相邻的一名队友获得[嘲讽]，直到回合结束。</t>
+  </si>
+  <si>
+    <t>能站在后排输出的角色</t>
+  </si>
+  <si>
+    <t>操控敌人打谁</t>
+  </si>
+  <si>
+    <t>反伤机兵</t>
+  </si>
+  <si>
+    <t>近战不敢碰</t>
+  </si>
+  <si>
+    <t>荆棘卫士</t>
+  </si>
+  <si>
+    <t>受到远程攻击时，对攻击者造成2点伤害。</t>
+  </si>
+  <si>
+    <t>能提供治疗的角色</t>
+  </si>
+  <si>
+    <t>白游侠、坠炮手、风语者、烈焰祭司</t>
+  </si>
+  <si>
+    <t>影丸、火枪手、战锤</t>
+  </si>
+  <si>
+    <t>远程不敢点</t>
+  </si>
+  <si>
+    <t>鼠队长、死灵法师、猎颅者、白游侠</t>
+  </si>
+  <si>
+    <t>免疫小伤害</t>
+  </si>
+  <si>
+    <t>冰霜守卫</t>
+  </si>
+  <si>
+    <t>被攻击后，令攻击者获得[冰冻]，直到其回合结束。</t>
+  </si>
+  <si>
+    <t>医护兵、德鲁伊</t>
+  </si>
+  <si>
+    <t>挨打就冻住对方</t>
+  </si>
+  <si>
+    <t>盾击兵</t>
+  </si>
+  <si>
+    <t>攻击后，将目标击退1格。</t>
+  </si>
+  <si>
+    <t>盾撞击退</t>
+  </si>
+  <si>
+    <t>守株待兔回血</t>
+  </si>
+  <si>
+    <t>哨兵</t>
+  </si>
+  <si>
+    <t>若本回合没有攻击，回合结束时获得[圣盾]。</t>
+  </si>
+  <si>
+    <t>打或守的抉择</t>
+  </si>
+  <si>
+    <t>掩护后排</t>
+  </si>
+  <si>
+    <t>死了也给全队加攻</t>
+  </si>
+  <si>
+    <t>全队解状态</t>
+  </si>
+  <si>
+    <t>攻击后，令目标无法回复HP，直到对方回合结束。</t>
+  </si>
+  <si>
+    <t>掐断回血</t>
+  </si>
+  <si>
+    <t>战地医师</t>
+  </si>
+  <si>
+    <t>己方回合结束时，治疗相邻的所有队友2点HP。</t>
+  </si>
+  <si>
+    <t>抱团才回血</t>
+  </si>
+  <si>
+    <t>鲜血祭司</t>
+  </si>
+  <si>
+    <t>攻击后，回复相邻队友3点HP。</t>
+  </si>
+  <si>
+    <t>边打边奶</t>
+  </si>
+  <si>
+    <t>圣盾工匠</t>
+  </si>
+  <si>
+    <t>己方回合开始时，令相邻的一名队友获得[圣盾]。</t>
+  </si>
+  <si>
+    <t>贴着谁谁有盾</t>
+  </si>
+  <si>
+    <t>战吼者</t>
+  </si>
+  <si>
+    <t>攻击后，令相邻的队友攻击力+1，直到回合结束。</t>
+  </si>
+  <si>
+    <t>冲上去开团</t>
+  </si>
+  <si>
+    <t>面板攻6空档</t>
+  </si>
+  <si>
+    <t>5攻疾行空档</t>
+  </si>
+  <si>
+    <t>渗透直取后排</t>
+  </si>
+  <si>
+    <t>4攻远程空档</t>
+  </si>
+  <si>
+    <t>玩法定位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇淑女、烛火x3、圣光、复仇者、暗域、古灵精怪、嬉皮死神、涌电技师、红帽x2、宿魂、共鸣者x3、荆棘树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬉皮死神×3、烛火×2、炸弹人×2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影丸、火枪手、赏金猎人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嬉皮死神×3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毒蛇淑女、白游侠、小阴影、烛火、长剑、赏金猎人、圣光、复仇者、暗域x2、嬉皮死神、长角、沉默术士、黄金矿工、风语者、宿魂、共鸣者、荆棘树人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影丸、烈焰祭司、沉默术士、风语者、坠炮手x3、涌电技师</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2828,6 +3456,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2839,12 +3473,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3139,7 +3767,7 @@
     <col min="7" max="7" width="34.375" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.25" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.875" style="27" customWidth="1"/>
-    <col min="10" max="10" width="9" style="7"/>
+    <col min="10" max="10" width="14.875" style="7" customWidth="1"/>
     <col min="11" max="11" width="9" style="7" customWidth="1"/>
     <col min="12" max="13" width="9" style="7"/>
     <col min="14" max="14" width="10.5" style="7" customWidth="1"/>
@@ -3468,7 +4096,7 @@
         <v>156</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>223</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -4083,7 +4711,7 @@
         <v>164</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4193,7 +4821,7 @@
         <v>156</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="57" x14ac:dyDescent="0.2">
@@ -4222,7 +4850,7 @@
         <v>28</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -4302,7 +4930,7 @@
         <v>156</v>
       </c>
       <c r="S22" s="27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4357,7 +4985,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -4381,7 +5009,9 @@
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="J24" s="11" t="s">
+        <v>444</v>
+      </c>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
         <f t="shared" si="0"/>
@@ -4610,7 +5240,7 @@
         <v>156</v>
       </c>
       <c r="S28" s="27" t="s">
-        <v>227</v>
+        <v>445</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="103.5" x14ac:dyDescent="0.2">
@@ -4663,7 +5293,7 @@
         <v>164</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>228</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -4765,7 +5395,7 @@
         <v>164</v>
       </c>
       <c r="S31" s="27" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
@@ -4918,7 +5548,7 @@
         <v>164</v>
       </c>
       <c r="S34" s="27" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
@@ -4947,7 +5577,7 @@
         <v>125</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>234</v>
+        <v>442</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5460,7 +6090,7 @@
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="28" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -5512,7 +6142,7 @@
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
+      <c r="J46" s="11"/>
       <c r="K46" s="9"/>
       <c r="L46" s="10">
         <f t="shared" si="4"/>
@@ -5562,7 +6192,7 @@
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="28" t="s">
-        <v>235</v>
+        <v>447</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -5642,7 +6272,7 @@
         <v>164</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -5719,7 +6349,7 @@
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="28" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -5818,14 +6448,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BBE2D7C-DF0B-49B4-9FE7-BB09A920D14C}">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="7" max="7" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.5" style="28" customWidth="1"/>
+    <col min="8" max="8" width="20.5" style="28" customWidth="1"/>
+    <col min="9" max="9" width="9" style="28"/>
+    <col min="10" max="10" width="27.625" style="28" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="0" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="13.875" style="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -5883,379 +6518,296 @@
       <c r="S1" s="27" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T1" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>50</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">兽族</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">狗头军师</t>
-        </is>
+      <c r="B2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C2" t="s">
+        <v>335</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>22</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">我方回合中，站在狗头军师相邻的队友攻击力+1。</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需要攻击力加成的角色</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白游侠、烛火、长剑、末日</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>336</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>325</v>
       </c>
       <c r="L2">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="M2">
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>4.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q2">
-        <v>18.7</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">嬉皮死神×2、小阴影、长角、共鸣者</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+        <v>17.8</v>
+      </c>
+      <c r="R2" t="s">
+        <v>238</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="T2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>51</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">兽族</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">狂徒</t>
-        </is>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>338</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>13</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最好搭配一个坦克</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>289</v>
       </c>
       <c r="L3">
-        <v>19.05</v>
+        <v>15.2</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q3">
-        <v>19.05</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白板</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔盾、圣光、复仇者</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R3" t="s">
+        <v>238</v>
+      </c>
+      <c r="S3" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="T3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>52</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">兽族</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">拾荒者</t>
-        </is>
+      <c r="B4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" t="s">
+        <v>341</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;疾行&gt;</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">拾取增益道具或金矿时，额外永久获得1点攻击力（最多+3）。</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能产生道具或金矿的角色</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、暗域、宿魂</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣诞老人、黄金矿工</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>342</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>242</v>
       </c>
       <c r="L4">
-        <v>13.4</v>
+        <v>15.2</v>
       </c>
       <c r="M4">
-        <v>1.5</v>
+        <v>-1</v>
       </c>
       <c r="N4">
         <v>2</v>
       </c>
       <c r="O4">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q4">
-        <v>19.3</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输出</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣诞老人、黄金矿工、风语者</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R4" t="s">
+        <v>239</v>
+      </c>
+      <c r="S4" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="T4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>53</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">兽族</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">图腾师</t>
-        </is>
+      <c r="B5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" t="s">
+        <v>344</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5">
-        <v>32</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">己方回合开始时，在相邻空地立一根图腾（耐久3，同时最多2根）。与图腾相邻的己方单位受到攻击伤害-1。</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需要保护的远程角色</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">伐木工、烛火、末日、白游侠</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="L5">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="O5">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q5">
-        <v>18.4</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">肉盾</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、医护兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19.3</v>
+      </c>
+      <c r="R5" t="s">
+        <v>238</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>320</v>
+      </c>
+      <c r="T5" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>54</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">兽族</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">血牙斗士</t>
-        </is>
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C6" t="s">
+        <v>347</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>24</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;嘲讽&gt;</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">每受到一次伤害，攻击力+1，直到我方回合结束。</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能治疗自己的角色</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">鼠队长、白游侠、死灵法师</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">赏金猎人、影丸、红帽</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>293</v>
       </c>
       <c r="L6">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6">
-        <v>4.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q6">
-        <v>18.6</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">肉盾</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医护兵、德鲁伊、圣光</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+        <v>17.8</v>
+      </c>
+      <c r="R6" t="s">
+        <v>238</v>
+      </c>
+      <c r="S6" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="T6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>55</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机械</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">拆弹手</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" t="s">
+        <v>326</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>19</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">移动后，拆除相邻格上的敌方炸弹，每拆除一颗回复4点HP；不会受到炸弹伤害。</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需要贴身保护的角色</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">炸弹人</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、鼠队长</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>245</v>
       </c>
       <c r="L7">
-        <v>15.15</v>
+        <v>14.7</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -6267,198 +6819,151 @@
         <v>3.3</v>
       </c>
       <c r="Q7">
-        <v>18.45</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔盾、独脚龟</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="R7" t="s">
+        <v>238</v>
+      </c>
+      <c r="S7" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="T7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>56</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机械</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">破盾锤</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" t="s">
+        <v>352</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">攻击无视目标的[圣盾]；若目标带有[圣盾]，本次伤害翻倍。</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能提供攻击力加成的角色</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">波盾、圣光</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔盾、独脚龟、装甲堡垒</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>353</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>249</v>
       </c>
       <c r="L8">
-        <v>15.6</v>
+        <v>16.45</v>
       </c>
       <c r="M8">
         <v>0</v>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8">
-        <v>4.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q8">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="R8" t="s">
+        <v>238</v>
+      </c>
+      <c r="S8" s="28" t="s">
+        <v>319</v>
+      </c>
+      <c r="T8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
         <v>20</v>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输出</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">烈焰祭司、圣诞老人</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>57</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机械</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">铆钉机兵</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>31</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;嘲讽&gt;</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">受到近战攻击时，对攻击者造成2点伤害。</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能提供圣盾或治疗的角色</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">鼠队长、太阳斩、嬉皮死神</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
-        </is>
+      <c r="G9" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>249</v>
       </c>
       <c r="L9">
-        <v>16.15</v>
+        <v>15.6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>2</v>
       </c>
       <c r="O9">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q9">
-        <v>19.55</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">肉盾</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">圣光、荆棘树人</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="R9" t="s">
+        <v>238</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="T9" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>58</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机械</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">绊线工兵</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C10" t="s">
+        <v>356</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>17</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">移动后，可在相邻空格布设一条绊线；敌人经过或停留时触发，获得[眩晕]，触发后消失。</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能使敌人位移的角色</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">坠炮手、宿魂、影丸</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>314</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>245</v>
       </c>
       <c r="L10">
-        <v>14.25</v>
+        <v>14.3</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -6467,487 +6972,1751 @@
         <v>2</v>
       </c>
       <c r="O10">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q10">
-        <v>18.65</v>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">傀儡师、超新星、长角、血锁</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+        <v>18.7</v>
+      </c>
+      <c r="R10" t="s">
+        <v>238</v>
+      </c>
+      <c r="S10" s="28" t="s">
+        <v>315</v>
+      </c>
+      <c r="T10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>59</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">机械</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">哨戒机</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" t="s">
+        <v>288</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>22</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">最好搭配一个坦克</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">暗域、宿魂、影丸</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="J11" s="28" t="s">
+        <v>277</v>
       </c>
       <c r="L11">
-        <v>18.7</v>
+        <v>14.7</v>
       </c>
       <c r="M11">
         <v>0</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
-        <v>18.7</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白板</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔盾、独脚龟</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="R11" t="s">
+        <v>238</v>
+      </c>
+      <c r="S11" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="T11" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>60</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">精灵</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">净化祭司</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
+        <v>281</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E12">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="H12" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L12">
+        <v>16</v>
+      </c>
+      <c r="M12">
+        <v>1.5</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q12">
+        <v>19.7</v>
+      </c>
+      <c r="R12" t="s">
+        <v>238</v>
+      </c>
+      <c r="S12" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="T12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C13" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
         <v>18</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">己方回合开始时，清除所有队友身上的负面状态；每清除一个，本回合自身攻击力+1（最多+3）。</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">需要站在前排的角色</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">战锤、雪拳、巨剑、沉默术士、荆棘树人、宿魂、猎颅者、白游侠</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、毒蛇淑女</t>
-        </is>
-      </c>
-      <c r="L12">
-        <v>12.5</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>3</v>
-      </c>
-      <c r="O12">
-        <v>6.6</v>
-      </c>
-      <c r="Q12">
-        <v>19.1</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">塔盾、装甲堡垒、独脚龟</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>61</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">精灵</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">卸力僧</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13">
-        <v>22</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">攻击后，令目标本回合无法反击。自身反击时造成2倍伤害。</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能提供攻击力加成的角色</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">复仇者、塔盾、装甲堡垒、荆棘树人、战锤、负墟</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、坠炮手</t>
-        </is>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="L13">
-        <v>14.3</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N13">
         <v>2</v>
       </c>
       <c r="O13">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q13">
-        <v>18.7</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">肉盾</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">医护兵、德鲁伊、风语者</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19.3</v>
+      </c>
+      <c r="R13" t="s">
+        <v>238</v>
+      </c>
+      <c r="S13" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="T13" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>62</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">精灵</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">霜语者</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="B14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" t="s">
+        <v>367</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>26</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">己方回合开始时，令所有敌人获得[冰冻]，对方回合结束时解除。</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">近战角色</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">风语者、影丸、鼠队长</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">负墟</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="I14" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="J14" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="L14">
-        <v>13.9</v>
+        <v>15.6</v>
       </c>
       <c r="M14">
         <v>0</v>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q14">
-        <v>18.3</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">长剑、暗域、大骑士</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+        <v>17.8</v>
+      </c>
+      <c r="R14" t="s">
+        <v>238</v>
+      </c>
+      <c r="S14" s="28" t="s">
+        <v>370</v>
+      </c>
+      <c r="T14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>63</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">魔族</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">掘墓人</t>
-        </is>
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" t="s">
+        <v>299</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
       <c r="E15">
-        <v>20</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">移动后，摧毁相邻的敌方墓碑（该格不能再被替补落位）；若相邻的是己方墓碑，改为回复6点HP。</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能提供攻击力加成的角色</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">波盾、太阳斩、猎颅者、梅林</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、火枪手、鼠队长</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>302</v>
       </c>
       <c r="L15">
-        <v>15.6</v>
+        <v>14.25</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q15">
-        <v>18.9</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">红帽、嬉皮死神、暗域</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+        <v>19.649999999999999</v>
+      </c>
+      <c r="R15" t="s">
+        <v>238</v>
+      </c>
+      <c r="S15" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="T15" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>64</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">魔族</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">瘟疫使者</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="B16" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" t="s">
+        <v>296</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>21</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">攻击后，令目标无法回复HP，直到对方回合结束；若目标已带有任意负面状态，额外造成3点无视圣盾的伤害。</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">能施加负面状态的角色</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">德鲁伊、医护兵、梅林、古拉博士、塔盾、复仇者、风语者</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">负墟、圣光</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>294</v>
       </c>
       <c r="L16">
-        <v>13.85</v>
+        <v>16.5</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16">
-        <v>4.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="Q16">
-        <v>18.25</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">输出</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">毒蛇淑女、战锤、雪拳、巨剑、荆棘树人、沉默术士</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+        <v>18.7</v>
+      </c>
+      <c r="R16" t="s">
+        <v>239</v>
+      </c>
+      <c r="S16" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="T16" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>65</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">人族</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">号令官</t>
-        </is>
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>244</v>
+      </c>
+      <c r="C17" t="s">
+        <v>375</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>24</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;远程&gt;</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">我方回合开始时，令相邻队友本回合首次攻击的伤害+2。</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">高攻击力或高倍率的角色</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">白游侠、烛火、末日</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>323</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>324</v>
       </c>
       <c r="L17">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17">
+        <v>2</v>
+      </c>
+      <c r="O17">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q17">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R17" t="s">
+        <v>238</v>
+      </c>
+      <c r="S17" s="28" t="s">
+        <v>325</v>
+      </c>
+      <c r="T17" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>24</v>
+      </c>
+      <c r="G18" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L18">
+        <v>15.2</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>2</v>
+      </c>
+      <c r="O18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q18">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R18" t="s">
+        <v>233</v>
+      </c>
+      <c r="S18" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="T18" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>257</v>
+      </c>
+      <c r="C19" t="s">
+        <v>383</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>22</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>385</v>
+      </c>
+      <c r="L19">
+        <v>16.5</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q19">
+        <v>18.7</v>
+      </c>
+      <c r="R19" t="s">
+        <v>238</v>
+      </c>
+      <c r="S19" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="T19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>257</v>
+      </c>
+      <c r="C20" t="s">
+        <v>387</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>26</v>
+      </c>
+      <c r="G20" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="H20" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="L20">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q20">
+        <v>18.3</v>
+      </c>
+      <c r="R20" t="s">
+        <v>233</v>
+      </c>
+      <c r="S20" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="T20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>257</v>
+      </c>
+      <c r="C21" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="H21" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="I21" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="J21" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="L21">
+        <v>14.8</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>2</v>
+      </c>
+      <c r="O21">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q21">
+        <v>19.2</v>
+      </c>
+      <c r="R21" t="s">
+        <v>233</v>
+      </c>
+      <c r="S21" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="T21" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="171" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" t="s">
+        <v>391</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>24</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="I22" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L22">
+        <v>15.2</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>2</v>
+      </c>
+      <c r="O22">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q22">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R22" t="s">
+        <v>233</v>
+      </c>
+      <c r="S22" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="T22" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" t="s">
+        <v>395</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="J23" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="L23">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M23">
+        <v>-1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q23">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R23" t="s">
+        <v>239</v>
+      </c>
+      <c r="S23" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="T23" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C24" t="s">
+        <v>399</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>31</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="I24" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L24">
+        <v>16.149999999999999</v>
+      </c>
+      <c r="M24">
+        <v>-1</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q24">
+        <v>19.55</v>
+      </c>
+      <c r="R24" t="s">
+        <v>239</v>
+      </c>
+      <c r="S24" s="28" t="s">
+        <v>254</v>
+      </c>
+      <c r="T24" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" ht="57" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>77</v>
+      </c>
+      <c r="B25" t="s">
+        <v>257</v>
+      </c>
+      <c r="C25" t="s">
+        <v>401</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>26</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>402</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="I25" s="28" t="s">
+        <v>404</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="L25">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q25">
+        <v>18.3</v>
+      </c>
+      <c r="R25" t="s">
+        <v>239</v>
+      </c>
+      <c r="S25" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="T25" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="57" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
+        <v>279</v>
+      </c>
+      <c r="C26" t="s">
+        <v>332</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J26" s="28" t="s">
+        <v>334</v>
+      </c>
+      <c r="L26">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M26">
+        <v>-1</v>
+      </c>
+      <c r="N26">
+        <v>3</v>
+      </c>
+      <c r="O26">
+        <v>1.35</v>
+      </c>
+      <c r="Q26">
+        <v>18.25</v>
+      </c>
+      <c r="R26" t="s">
+        <v>239</v>
+      </c>
+      <c r="S26" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="T26" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>79</v>
+      </c>
+      <c r="B27" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>22</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="J27" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L27">
+        <v>14.3</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>2</v>
+      </c>
+      <c r="O27">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q27">
+        <v>18.7</v>
+      </c>
+      <c r="R27" t="s">
+        <v>239</v>
+      </c>
+      <c r="S27" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="T27" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" t="s">
+        <v>409</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>32</v>
+      </c>
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="H28" s="28" t="s">
+        <v>403</v>
+      </c>
+      <c r="I28" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="J28" s="28" t="s">
+        <v>316</v>
+      </c>
+      <c r="L28">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M28">
+        <v>-1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q28">
+        <v>17.8</v>
+      </c>
+      <c r="R28" t="s">
+        <v>239</v>
+      </c>
+      <c r="S28" s="28" t="s">
+        <v>411</v>
+      </c>
+      <c r="T28" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>232</v>
+      </c>
+      <c r="C29" t="s">
+        <v>413</v>
+      </c>
+      <c r="D29">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>30</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="28" t="s">
+        <v>414</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="L29">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M29">
+        <v>-1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q29">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R29" t="s">
+        <v>239</v>
+      </c>
+      <c r="S29" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="T29" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>82</v>
+      </c>
+      <c r="B30" t="s">
+        <v>232</v>
+      </c>
+      <c r="C30" t="s">
+        <v>283</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>284</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="J30" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="L30">
+        <v>17.95</v>
+      </c>
+      <c r="M30">
+        <v>-1</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>2.25</v>
+      </c>
+      <c r="Q30">
+        <v>19.2</v>
+      </c>
+      <c r="R30" t="s">
+        <v>239</v>
+      </c>
+      <c r="S30" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="T30" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>279</v>
+      </c>
+      <c r="C31" t="s">
+        <v>417</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>24</v>
+      </c>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>418</v>
+      </c>
+      <c r="H31" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="L31">
+        <v>15.2</v>
+      </c>
+      <c r="M31">
+        <v>-1</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q31">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R31" t="s">
+        <v>239</v>
+      </c>
+      <c r="S31" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="T31" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>84</v>
+      </c>
+      <c r="B32" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>36</v>
+      </c>
+      <c r="F32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="H32" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="I32" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="J32" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="L32">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M32">
+        <v>-1</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>1.35</v>
+      </c>
+      <c r="Q32">
+        <v>18.75</v>
+      </c>
+      <c r="R32" t="s">
+        <v>239</v>
+      </c>
+      <c r="S32" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="T32" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>85</v>
+      </c>
+      <c r="B33" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" t="s">
+        <v>328</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>329</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="J33" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="L33">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M33">
+        <v>-1</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q33">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R33" t="s">
+        <v>239</v>
+      </c>
+      <c r="S33" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="T33" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="114" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>86</v>
+      </c>
+      <c r="B34" t="s">
+        <v>257</v>
+      </c>
+      <c r="C34" t="s">
+        <v>258</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>18</v>
+      </c>
+      <c r="F34" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="H34" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="I34" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="L34">
+        <v>12.5</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>3</v>
+      </c>
+      <c r="O34">
+        <v>6.6</v>
+      </c>
+      <c r="Q34">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R34" t="s">
+        <v>233</v>
+      </c>
+      <c r="S34" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="T34" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>273</v>
+      </c>
+      <c r="C35" t="s">
+        <v>274</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35">
+        <v>21</v>
+      </c>
+      <c r="G35" s="28" t="s">
+        <v>423</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="I35" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="J35" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="L35">
+        <v>13.85</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="O35">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q35">
+        <v>18.25</v>
+      </c>
+      <c r="R35" t="s">
+        <v>238</v>
+      </c>
+      <c r="S35" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="T35" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>88</v>
+      </c>
+      <c r="B36" t="s">
+        <v>279</v>
+      </c>
+      <c r="C36" t="s">
+        <v>425</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>28</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="28" t="s">
+        <v>426</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="L36">
+        <v>17</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>1.35</v>
+      </c>
+      <c r="Q36">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="R36" t="s">
+        <v>233</v>
+      </c>
+      <c r="S36" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="T36" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>89</v>
+      </c>
+      <c r="B37" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" t="s">
+        <v>428</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <v>24</v>
+      </c>
+      <c r="G37" s="28" t="s">
+        <v>429</v>
+      </c>
+      <c r="H37" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="J37" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="L37">
+        <v>15.2</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
+      </c>
+      <c r="O37">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q37">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R37" t="s">
+        <v>233</v>
+      </c>
+      <c r="S37" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="T37" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>90</v>
+      </c>
+      <c r="B38" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" t="s">
+        <v>431</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="28" t="s">
+        <v>432</v>
+      </c>
+      <c r="H38" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="L38">
+        <v>15.7</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
         <v>1.5</v>
       </c>
-      <c r="O17">
+      <c r="O38">
         <v>3.3</v>
       </c>
-      <c r="Q17">
-        <v>18.5</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">辅助</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">影丸、红帽、鼠队长、小阴影</t>
-        </is>
+      <c r="Q38">
+        <v>19</v>
+      </c>
+      <c r="R38" t="s">
+        <v>233</v>
+      </c>
+      <c r="S38" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="T38" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
+        <v>232</v>
+      </c>
+      <c r="C39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>20</v>
+      </c>
+      <c r="G39" s="28" t="s">
+        <v>435</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="L39">
+        <v>15.6</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>1.5</v>
+      </c>
+      <c r="O39">
+        <v>3.3</v>
+      </c>
+      <c r="Q39">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="R39" t="s">
+        <v>233</v>
+      </c>
+      <c r="S39" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="T39" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>92</v>
+      </c>
+      <c r="B40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" t="s">
+        <v>234</v>
+      </c>
+      <c r="D40">
+        <v>6</v>
+      </c>
+      <c r="E40">
+        <v>13</v>
+      </c>
+      <c r="F40" s="28"/>
+      <c r="H40" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J40" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L40">
+        <v>19.05</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>19.05</v>
+      </c>
+      <c r="R40" t="s">
+        <v>236</v>
+      </c>
+      <c r="S40" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="T40" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>93</v>
+      </c>
+      <c r="B41" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" t="s">
+        <v>291</v>
+      </c>
+      <c r="D41">
+        <v>5</v>
+      </c>
+      <c r="E41">
+        <v>14</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L41">
+        <v>17.3</v>
+      </c>
+      <c r="M41">
+        <v>1.5</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>18.8</v>
+      </c>
+      <c r="R41" t="s">
+        <v>236</v>
+      </c>
+      <c r="S41" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="T41" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>94</v>
+      </c>
+      <c r="B42" t="s">
+        <v>273</v>
+      </c>
+      <c r="C42" t="s">
+        <v>321</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42">
+        <v>13</v>
+      </c>
+      <c r="F42" t="s">
+        <v>96</v>
+      </c>
+      <c r="H42" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M42">
+        <v>1.5</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="R42" t="s">
+        <v>236</v>
+      </c>
+      <c r="S42" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="T42" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>95</v>
+      </c>
+      <c r="B43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" t="s">
+        <v>255</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="E43">
+        <v>22</v>
+      </c>
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" s="28" t="s">
+        <v>256</v>
+      </c>
+      <c r="L43">
+        <v>18.7</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>18.7</v>
+      </c>
+      <c r="R43" t="s">
+        <v>236</v>
+      </c>
+      <c r="S43" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="T43" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -6962,10 +8731,10 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="30"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -7082,30 +8851,30 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
     </row>
     <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -7259,14 +9028,14 @@
     </row>
     <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
     </row>
     <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
@@ -7522,14 +9291,14 @@
       <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Data/Hero/角色列表.xlsx
+++ b/Data/Hero/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\Data\Hero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38CB8C1D-50C9-4258-9750-3837CC9E2A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D78144-F394-4D2E-A59F-E7D3C3B58599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="3705" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">角色列表!$A$1:$R$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="450">
   <si>
     <t>No.</t>
   </si>
@@ -303,9 +302,6 @@
   </si>
   <si>
     <t>黄金矿工</t>
-  </si>
-  <si>
-    <t>所有其他队友获得&lt;疾行&gt;，且移动后回复等同于本次移动距离的HP。</t>
   </si>
   <si>
     <t>负墟</t>
@@ -3133,6 +3129,76 @@
   </si>
   <si>
     <t>影丸、烈焰祭司、沉默术士、风语者、坠炮手x3、涌电技师</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>风语者在场时，所有其他队友获得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>风语</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动力+1，移动时恢复移动格子的生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>风语</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3781,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -3811,28 +3877,28 @@
         <v>9</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P1" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="R1" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -3840,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>10</v>
@@ -3882,7 +3948,7 @@
         <v>18.75</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="69" x14ac:dyDescent="0.2">
@@ -3890,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>13</v>
@@ -3905,7 +3971,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>15</v>
@@ -3936,10 +4002,10 @@
         <v>17.700000000000003</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -3947,7 +4013,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>16</v>
@@ -3991,10 +4057,10 @@
         <v>18.250000000000004</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4002,7 +4068,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>18</v>
@@ -4042,7 +4108,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -4050,7 +4116,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>19</v>
@@ -4065,7 +4131,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>21</v>
@@ -4093,10 +4159,10 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R6" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -4104,7 +4170,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>22</v>
@@ -4116,7 +4182,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>23</v>
@@ -4148,7 +4214,7 @@
         <v>16.650000000000002</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S7" s="9"/>
     </row>
@@ -4157,7 +4223,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>25</v>
@@ -4169,7 +4235,7 @@
         <v>14</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="9" t="s">
@@ -4197,7 +4263,7 @@
         <v>18.8</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S8" s="9"/>
     </row>
@@ -4206,7 +4272,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>27</v>
@@ -4221,7 +4287,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
@@ -4250,10 +4316,10 @@
         <v>15.200000000000001</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4261,7 +4327,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>29</v>
@@ -4299,7 +4365,7 @@
         <v>17.8</v>
       </c>
       <c r="R10" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -4307,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>30</v>
@@ -4319,7 +4385,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>31</v>
@@ -4351,10 +4417,10 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4362,7 +4428,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>32</v>
@@ -4404,7 +4470,7 @@
         <v>19.2</v>
       </c>
       <c r="R12" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4412,7 +4478,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>35</v>
@@ -4454,7 +4520,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R13" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4462,7 +4528,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>38</v>
@@ -4502,7 +4568,7 @@
         <v>18.25</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -4510,7 +4576,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>39</v>
@@ -4552,7 +4618,7 @@
         <v>17.350000000000001</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S15" s="9"/>
     </row>
@@ -4561,7 +4627,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>42</v>
@@ -4605,7 +4671,7 @@
         <v>19.5</v>
       </c>
       <c r="R16" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S16" s="12"/>
     </row>
@@ -4614,7 +4680,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>44</v>
@@ -4656,7 +4722,7 @@
         <v>18.7</v>
       </c>
       <c r="R17" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -4664,7 +4730,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>47</v>
@@ -4676,13 +4742,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>48</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -4708,10 +4774,10 @@
         <v>21.15</v>
       </c>
       <c r="R18" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4719,7 +4785,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>49</v>
@@ -4763,7 +4829,7 @@
         <v>20.6</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S19" s="9" t="s">
         <v>47</v>
@@ -4774,7 +4840,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>51</v>
@@ -4818,10 +4884,10 @@
         <v>16.900000000000002</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="57" x14ac:dyDescent="0.2">
@@ -4829,7 +4895,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>54</v>
@@ -4841,16 +4907,16 @@
         <v>19</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -4875,7 +4941,7 @@
         <v>19.550000000000004</v>
       </c>
       <c r="R21" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S21" s="9"/>
     </row>
@@ -4884,7 +4950,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>55</v>
@@ -4927,10 +4993,10 @@
         <v>18.450000000000003</v>
       </c>
       <c r="R22" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S22" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4938,7 +5004,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>58</v>
@@ -4953,7 +5019,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="11"/>
@@ -4982,7 +5048,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="R23" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="28.5" x14ac:dyDescent="0.2">
@@ -4990,7 +5056,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>59</v>
@@ -5010,7 +5076,7 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
@@ -5034,7 +5100,7 @@
         <v>19.5</v>
       </c>
       <c r="R24" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -5042,7 +5108,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>61</v>
@@ -5057,7 +5123,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -5084,7 +5150,7 @@
         <v>17.25</v>
       </c>
       <c r="R25" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5092,7 +5158,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>63</v>
@@ -5107,7 +5173,7 @@
         <v>33</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="28" t="s">
@@ -5136,7 +5202,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R26" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5144,7 +5210,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>64</v>
@@ -5156,7 +5222,7 @@
         <v>26</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G27" s="20" t="s">
         <v>65</v>
@@ -5186,7 +5252,7 @@
         <v>18.8</v>
       </c>
       <c r="R27" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5194,7 +5260,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>66</v>
@@ -5206,7 +5272,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>67</v>
@@ -5237,10 +5303,10 @@
         <v>21.900000000000002</v>
       </c>
       <c r="R28" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S28" s="27" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="103.5" x14ac:dyDescent="0.2">
@@ -5248,7 +5314,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>69</v>
@@ -5261,10 +5327,10 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -5290,10 +5356,10 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5301,7 +5367,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>70</v>
@@ -5313,7 +5379,7 @@
         <v>16</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G30" s="20" t="s">
         <v>71</v>
@@ -5343,7 +5409,7 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R30" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="69" x14ac:dyDescent="0.2">
@@ -5351,7 +5417,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>68</v>
@@ -5367,7 +5433,7 @@
         <v>72</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -5392,10 +5458,10 @@
         <v>20</v>
       </c>
       <c r="R31" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S31" s="27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
@@ -5403,7 +5469,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>73</v>
@@ -5418,7 +5484,7 @@
         <v>74</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -5445,7 +5511,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="R32" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5453,7 +5519,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>75</v>
@@ -5494,7 +5560,7 @@
         <v>18.5</v>
       </c>
       <c r="R33" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5502,7 +5568,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>37</v>
@@ -5517,7 +5583,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>77</v>
@@ -5545,10 +5611,10 @@
         <v>15.8</v>
       </c>
       <c r="R34" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S34" s="27" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
@@ -5556,7 +5622,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>78</v>
@@ -5568,16 +5634,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G35" s="20" t="s">
         <v>79</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5602,7 +5668,7 @@
         <v>21.450000000000003</v>
       </c>
       <c r="R35" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S35" s="9"/>
     </row>
@@ -5611,10 +5677,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>162</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>163</v>
       </c>
       <c r="D36" s="9">
         <v>3</v>
@@ -5626,10 +5692,10 @@
         <v>20</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
@@ -5655,10 +5721,10 @@
         <v>20</v>
       </c>
       <c r="R36" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5666,7 +5732,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>80</v>
@@ -5678,7 +5744,7 @@
         <v>20</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G37" s="20" t="s">
         <v>81</v>
@@ -5708,7 +5774,7 @@
         <v>16</v>
       </c>
       <c r="R37" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
@@ -5716,7 +5782,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>82</v>
@@ -5729,10 +5795,10 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -5758,10 +5824,10 @@
         <v>17.8</v>
       </c>
       <c r="R38" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5769,7 +5835,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>83</v>
@@ -5811,7 +5877,7 @@
         <v>17.55</v>
       </c>
       <c r="R39" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5819,7 +5885,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>85</v>
@@ -5861,7 +5927,7 @@
         <v>18.649999999999999</v>
       </c>
       <c r="R40" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5869,7 +5935,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>87</v>
@@ -5882,7 +5948,7 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="9"/>
@@ -5909,7 +5975,7 @@
         <v>21.25</v>
       </c>
       <c r="R41" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
@@ -5917,7 +5983,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>88</v>
@@ -5930,7 +5996,7 @@
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>57</v>
@@ -5958,10 +6024,10 @@
         <v>17.400000000000002</v>
       </c>
       <c r="R42" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S42" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
@@ -5969,7 +6035,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>89</v>
@@ -5984,7 +6050,7 @@
         <v>14</v>
       </c>
       <c r="G43" s="21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9"/>
@@ -6011,15 +6077,15 @@
         <v>20.6</v>
       </c>
       <c r="R43" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="32.25" x14ac:dyDescent="0.2">
       <c r="A44" s="9">
         <v>43</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>62</v>
@@ -6033,8 +6099,8 @@
       <c r="F44" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="G44" s="20" t="s">
-        <v>90</v>
+      <c r="G44" s="21" t="s">
+        <v>447</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -6063,7 +6129,7 @@
         <v>15.2</v>
       </c>
       <c r="R44" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -6071,10 +6137,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" s="9">
         <v>2</v>
@@ -6086,11 +6152,11 @@
         <v>33</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -6115,7 +6181,7 @@
         <v>19.5</v>
       </c>
       <c r="R45" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="60" x14ac:dyDescent="0.2">
@@ -6123,10 +6189,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" s="9">
         <v>3</v>
@@ -6138,7 +6204,7 @@
         <v>20</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9"/>
@@ -6165,7 +6231,7 @@
         <v>18.200000000000003</v>
       </c>
       <c r="R46" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
@@ -6173,10 +6239,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -6185,14 +6251,14 @@
         <v>19</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="28" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -6217,7 +6283,7 @@
         <v>18.850000000000001</v>
       </c>
       <c r="R47" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -6225,10 +6291,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D48" s="9">
         <v>0</v>
@@ -6240,10 +6306,10 @@
         <v>14</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
@@ -6269,10 +6335,10 @@
         <v>18.399999999999999</v>
       </c>
       <c r="R48" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -6280,10 +6346,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -6295,7 +6361,7 @@
         <v>33</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="9"/>
@@ -6322,7 +6388,7 @@
         <v>18.75</v>
       </c>
       <c r="R49" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="99.75" x14ac:dyDescent="0.2">
@@ -6330,10 +6396,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D50" s="4">
         <v>2</v>
@@ -6345,11 +6411,11 @@
         <v>33</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -6374,18 +6440,18 @@
         <v>17.3</v>
       </c>
       <c r="R50" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="C51" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
@@ -6395,7 +6461,7 @@
       </c>
       <c r="F51" s="9"/>
       <c r="G51" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="9"/>
@@ -6465,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>1</v>
@@ -6495,31 +6561,31 @@
         <v>9</v>
       </c>
       <c r="L1" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="M1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="P1" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>120</v>
-      </c>
       <c r="R1" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6527,10 +6593,10 @@
         <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -6542,13 +6608,13 @@
         <v>20</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L2">
         <v>15.6</v>
@@ -6566,13 +6632,13 @@
         <v>17.8</v>
       </c>
       <c r="R2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6580,10 +6646,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -6592,13 +6658,13 @@
         <v>24</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L3">
         <v>15.2</v>
@@ -6616,13 +6682,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="T3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -6630,10 +6696,10 @@
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -6645,16 +6711,16 @@
         <v>33</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H4" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="J4" s="28" t="s">
         <v>241</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>242</v>
       </c>
       <c r="L4">
         <v>15.2</v>
@@ -6672,13 +6738,13 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S4" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6686,10 +6752,10 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -6698,13 +6764,13 @@
         <v>16</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L5">
         <v>16</v>
@@ -6722,13 +6788,13 @@
         <v>19.3</v>
       </c>
       <c r="R5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S5" s="28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="T5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6736,10 +6802,10 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -6748,13 +6814,13 @@
         <v>20</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L6">
         <v>15.6</v>
@@ -6772,13 +6838,13 @@
         <v>17.8</v>
       </c>
       <c r="R6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S6" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="T6" t="s">
         <v>349</v>
-      </c>
-      <c r="T6" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6786,10 +6852,10 @@
         <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -6798,13 +6864,13 @@
         <v>18</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L7">
         <v>14.7</v>
@@ -6822,13 +6888,13 @@
         <v>18</v>
       </c>
       <c r="R7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S7" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6836,10 +6902,10 @@
         <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6848,13 +6914,13 @@
         <v>17</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L8">
         <v>16.45</v>
@@ -6872,13 +6938,13 @@
         <v>18.649999999999999</v>
       </c>
       <c r="R8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S8" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6886,10 +6952,10 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -6898,16 +6964,16 @@
         <v>20</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="J9" s="28" t="s">
         <v>248</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>249</v>
       </c>
       <c r="L9">
         <v>15.6</v>
@@ -6925,13 +6991,13 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S9" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6939,10 +7005,10 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -6954,13 +7020,13 @@
         <v>20</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="H10" s="28" t="s">
-        <v>314</v>
-      </c>
       <c r="J10" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L10">
         <v>14.3</v>
@@ -6978,13 +7044,13 @@
         <v>18.7</v>
       </c>
       <c r="R10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S10" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -6992,10 +7058,10 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -7007,13 +7073,13 @@
         <v>20</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L11">
         <v>14.7</v>
@@ -7031,13 +7097,13 @@
         <v>18</v>
       </c>
       <c r="R11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S11" s="28" t="s">
+        <v>358</v>
+      </c>
+      <c r="T11" t="s">
         <v>359</v>
-      </c>
-      <c r="T11" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -7045,10 +7111,10 @@
         <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -7060,13 +7126,13 @@
         <v>14</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L12">
         <v>16</v>
@@ -7084,13 +7150,13 @@
         <v>19.7</v>
       </c>
       <c r="R12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S12" s="28" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="T12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7098,10 +7164,10 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -7113,13 +7179,13 @@
         <v>14</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L13">
         <v>16.899999999999999</v>
@@ -7137,13 +7203,13 @@
         <v>19.3</v>
       </c>
       <c r="R13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S13" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="T13" t="s">
         <v>365</v>
-      </c>
-      <c r="T13" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7151,10 +7217,10 @@
         <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -7163,16 +7229,16 @@
         <v>20</v>
       </c>
       <c r="G14" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="I14" s="28" t="s">
         <v>368</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>369</v>
-      </c>
       <c r="J14" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L14">
         <v>15.6</v>
@@ -7190,13 +7256,13 @@
         <v>17.8</v>
       </c>
       <c r="R14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S14" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="T14" t="s">
         <v>370</v>
-      </c>
-      <c r="T14" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7204,10 +7270,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -7219,13 +7285,13 @@
         <v>74</v>
       </c>
       <c r="G15" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="J15" s="28" t="s">
         <v>301</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>302</v>
       </c>
       <c r="L15">
         <v>14.25</v>
@@ -7243,13 +7309,13 @@
         <v>19.649999999999999</v>
       </c>
       <c r="R15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S15" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T15" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7257,10 +7323,10 @@
         <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -7269,13 +7335,13 @@
         <v>22</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H16" s="28" t="s">
         <v>57</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L16">
         <v>16.5</v>
@@ -7293,13 +7359,13 @@
         <v>18.7</v>
       </c>
       <c r="R16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S16" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T16" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7307,10 +7373,10 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -7319,13 +7385,13 @@
         <v>18</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H17" s="28" t="s">
+        <v>322</v>
+      </c>
+      <c r="J17" s="28" t="s">
         <v>323</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>324</v>
       </c>
       <c r="L17">
         <v>14.7</v>
@@ -7343,13 +7409,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S17" s="28" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="T17" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7357,10 +7423,10 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C18" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -7369,13 +7435,13 @@
         <v>24</v>
       </c>
       <c r="G18" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="H18" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>380</v>
-      </c>
       <c r="J18" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L18">
         <v>15.2</v>
@@ -7393,13 +7459,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S18" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="T18" t="s">
         <v>381</v>
-      </c>
-      <c r="T18" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7407,10 +7473,10 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -7419,13 +7485,13 @@
         <v>22</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L19">
         <v>16.5</v>
@@ -7443,13 +7509,13 @@
         <v>18.7</v>
       </c>
       <c r="R19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S19" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="T19" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7457,10 +7523,10 @@
         <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C20" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -7469,13 +7535,13 @@
         <v>26</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H20" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L20">
         <v>16.100000000000001</v>
@@ -7493,13 +7559,13 @@
         <v>18.3</v>
       </c>
       <c r="R20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S20" s="28" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="T20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7507,10 +7573,10 @@
         <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7522,16 +7588,16 @@
         <v>20</v>
       </c>
       <c r="G21" s="28" t="s">
+        <v>268</v>
+      </c>
+      <c r="H21" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="I21" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="I21" s="28" t="s">
-        <v>271</v>
-      </c>
       <c r="J21" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>14.8</v>
@@ -7549,13 +7615,13 @@
         <v>19.2</v>
       </c>
       <c r="R21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S21" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T21" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="171" x14ac:dyDescent="0.2">
@@ -7563,10 +7629,10 @@
         <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C22" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -7575,16 +7641,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="H22" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>393</v>
-      </c>
       <c r="J22" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L22">
         <v>15.2</v>
@@ -7602,13 +7668,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S22" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T22" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7616,10 +7682,10 @@
         <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -7631,13 +7697,13 @@
         <v>33</v>
       </c>
       <c r="G23" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="H23" s="28" t="s">
         <v>396</v>
       </c>
-      <c r="H23" s="28" t="s">
-        <v>397</v>
-      </c>
       <c r="J23" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L23">
         <v>17.899999999999999</v>
@@ -7655,13 +7721,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S23" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="T23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7669,10 +7735,10 @@
         <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -7684,16 +7750,16 @@
         <v>33</v>
       </c>
       <c r="G24" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="H24" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="I24" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>253</v>
-      </c>
       <c r="J24" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L24">
         <v>16.149999999999999</v>
@@ -7711,13 +7777,13 @@
         <v>19.55</v>
       </c>
       <c r="R24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S24" s="28" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T24" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="57" x14ac:dyDescent="0.2">
@@ -7725,10 +7791,10 @@
         <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -7737,16 +7803,16 @@
         <v>26</v>
       </c>
       <c r="G25" s="28" t="s">
+        <v>401</v>
+      </c>
+      <c r="H25" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="I25" s="28" t="s">
         <v>403</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="J25" s="28" t="s">
         <v>404</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>405</v>
       </c>
       <c r="L25">
         <v>16.100000000000001</v>
@@ -7764,13 +7830,13 @@
         <v>18.3</v>
       </c>
       <c r="R25" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S25" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T25" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="57" x14ac:dyDescent="0.2">
@@ -7778,10 +7844,10 @@
         <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -7793,16 +7859,16 @@
         <v>33</v>
       </c>
       <c r="G26" s="28" t="s">
+        <v>332</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>406</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>333</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>240</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>407</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>334</v>
       </c>
       <c r="L26">
         <v>17.899999999999999</v>
@@ -7820,13 +7886,13 @@
         <v>18.25</v>
       </c>
       <c r="R26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S26" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="T26" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="85.5" x14ac:dyDescent="0.2">
@@ -7834,10 +7900,10 @@
         <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -7846,16 +7912,16 @@
         <v>22</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H27" s="28" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L27">
         <v>14.3</v>
@@ -7873,13 +7939,13 @@
         <v>18.7</v>
       </c>
       <c r="R27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S27" s="28" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7887,10 +7953,10 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -7902,16 +7968,16 @@
         <v>33</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L28">
         <v>16.600000000000001</v>
@@ -7929,13 +7995,13 @@
         <v>17.8</v>
       </c>
       <c r="R28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S28" s="28" t="s">
+        <v>410</v>
+      </c>
+      <c r="T28" t="s">
         <v>411</v>
-      </c>
-      <c r="T28" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7943,10 +8009,10 @@
         <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C29" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -7958,13 +8024,13 @@
         <v>33</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H29" s="28" t="s">
         <v>57</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L29">
         <v>17.899999999999999</v>
@@ -7982,13 +8048,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S29" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="T29" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7996,10 +8062,10 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -8011,13 +8077,13 @@
         <v>33</v>
       </c>
       <c r="G30" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="H30" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="J30" s="28" t="s">
         <v>285</v>
-      </c>
-      <c r="J30" s="28" t="s">
-        <v>286</v>
       </c>
       <c r="L30">
         <v>17.95</v>
@@ -8035,13 +8101,13 @@
         <v>19.2</v>
       </c>
       <c r="R30" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S30" s="28" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="T30" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8049,10 +8115,10 @@
         <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C31" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -8064,13 +8130,13 @@
         <v>33</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H31" s="28" t="s">
         <v>28</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L31">
         <v>15.2</v>
@@ -8088,13 +8154,13 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R31" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S31" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="T31" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -8102,10 +8168,10 @@
         <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -8117,16 +8183,16 @@
         <v>33</v>
       </c>
       <c r="G32" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="H32" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="I32" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="J32" s="28" t="s">
         <v>309</v>
-      </c>
-      <c r="J32" s="28" t="s">
-        <v>310</v>
       </c>
       <c r="L32">
         <v>18.399999999999999</v>
@@ -8144,13 +8210,13 @@
         <v>18.75</v>
       </c>
       <c r="R32" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="T32" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8158,10 +8224,10 @@
         <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -8173,13 +8239,13 @@
         <v>33</v>
       </c>
       <c r="G33" s="28" t="s">
+        <v>328</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="J33" s="28" t="s">
         <v>329</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>301</v>
-      </c>
-      <c r="J33" s="28" t="s">
-        <v>330</v>
       </c>
       <c r="L33">
         <v>17.899999999999999</v>
@@ -8197,13 +8263,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="S33" s="28" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="T33" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="114" x14ac:dyDescent="0.2">
@@ -8211,10 +8277,10 @@
         <v>86</v>
       </c>
       <c r="B34" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" t="s">
         <v>257</v>
-      </c>
-      <c r="C34" t="s">
-        <v>258</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -8226,16 +8292,16 @@
         <v>20</v>
       </c>
       <c r="G34" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="H34" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="I34" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="J34" s="28" t="s">
         <v>261</v>
-      </c>
-      <c r="J34" s="28" t="s">
-        <v>262</v>
       </c>
       <c r="L34">
         <v>12.5</v>
@@ -8253,13 +8319,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S34" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T34" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="99.75" x14ac:dyDescent="0.2">
@@ -8267,10 +8333,10 @@
         <v>87</v>
       </c>
       <c r="B35" t="s">
+        <v>272</v>
+      </c>
+      <c r="C35" t="s">
         <v>273</v>
-      </c>
-      <c r="C35" t="s">
-        <v>274</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -8279,16 +8345,16 @@
         <v>21</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H35" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="I35" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="J35" s="28" t="s">
         <v>276</v>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>277</v>
       </c>
       <c r="L35">
         <v>13.85</v>
@@ -8306,13 +8372,13 @@
         <v>18.25</v>
       </c>
       <c r="R35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S35" s="28" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="T35" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8320,10 +8386,10 @@
         <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C36" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -8335,13 +8401,13 @@
         <v>20</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L36">
         <v>17</v>
@@ -8359,13 +8425,13 @@
         <v>18.350000000000001</v>
       </c>
       <c r="R36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S36" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T36" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8373,10 +8439,10 @@
         <v>89</v>
       </c>
       <c r="B37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C37" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -8385,13 +8451,13 @@
         <v>24</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H37" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="J37" s="28" t="s">
         <v>292</v>
-      </c>
-      <c r="J37" s="28" t="s">
-        <v>293</v>
       </c>
       <c r="L37">
         <v>15.2</v>
@@ -8409,13 +8475,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R37" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S37" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="T37" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8423,10 +8489,10 @@
         <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C38" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -8438,13 +8504,13 @@
         <v>20</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J38" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L38">
         <v>15.7</v>
@@ -8462,13 +8528,13 @@
         <v>19</v>
       </c>
       <c r="R38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S38" s="28" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T38" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8476,10 +8542,10 @@
         <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C39" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -8488,13 +8554,13 @@
         <v>20</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H39" s="28" t="s">
         <v>53</v>
       </c>
       <c r="J39" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L39">
         <v>15.6</v>
@@ -8512,13 +8578,13 @@
         <v>18.899999999999999</v>
       </c>
       <c r="R39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S39" s="28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T39" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8526,10 +8592,10 @@
         <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D40">
         <v>6</v>
@@ -8542,7 +8608,7 @@
         <v>26</v>
       </c>
       <c r="J40" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L40">
         <v>19.05</v>
@@ -8560,13 +8626,13 @@
         <v>19.05</v>
       </c>
       <c r="R40" t="s">
+        <v>235</v>
+      </c>
+      <c r="S40" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="S40" s="28" t="s">
-        <v>237</v>
-      </c>
       <c r="T40" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8574,10 +8640,10 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -8592,7 +8658,7 @@
         <v>26</v>
       </c>
       <c r="J41" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L41">
         <v>17.3</v>
@@ -8610,13 +8676,13 @@
         <v>18.8</v>
       </c>
       <c r="R41" t="s">
+        <v>235</v>
+      </c>
+      <c r="S41" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="S41" s="28" t="s">
-        <v>237</v>
-      </c>
       <c r="T41" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8624,10 +8690,10 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C42" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -8636,13 +8702,13 @@
         <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H42" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J42" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L42">
         <v>16.850000000000001</v>
@@ -8660,13 +8726,13 @@
         <v>18.350000000000001</v>
       </c>
       <c r="R42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S42" s="28" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="T42" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
@@ -8674,10 +8740,10 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C43" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -8692,7 +8758,7 @@
         <v>26</v>
       </c>
       <c r="J43" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L43">
         <v>18.7</v>
@@ -8710,13 +8776,13 @@
         <v>18.7</v>
       </c>
       <c r="R43" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="S43" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T43" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -8732,21 +8798,21 @@
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B5" s="30"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A7)</f>
@@ -8755,7 +8821,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B8" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A8)</f>
@@ -8764,7 +8830,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B9" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A9)</f>
@@ -8773,7 +8839,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A10)</f>
@@ -8782,7 +8848,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11" s="3">
         <f>COUNTIF(角色列表!B:B,数据统计!A11)</f>
@@ -8794,15 +8860,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -8811,7 +8877,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -8820,7 +8886,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -8829,7 +8895,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A17)</f>
@@ -8847,12 +8913,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A54A7-3772-444D-AA2D-5E70DBC959BF}">
-  <dimension ref="A4:Q26"/>
+  <dimension ref="A4:Q27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="4" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A4" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
@@ -8868,7 +8934,7 @@
     </row>
     <row r="5" spans="1:17" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
@@ -8878,10 +8944,10 @@
     </row>
     <row r="6" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
@@ -8901,10 +8967,10 @@
     </row>
     <row r="7" spans="1:17" s="7" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -8913,10 +8979,10 @@
     </row>
     <row r="8" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -8936,10 +9002,10 @@
     </row>
     <row r="9" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -8959,10 +9025,10 @@
     </row>
     <row r="10" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -8982,10 +9048,10 @@
     </row>
     <row r="11" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -9005,10 +9071,10 @@
     </row>
     <row r="12" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -9029,7 +9095,7 @@
     <row r="13" spans="1:17" s="7" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:17" s="7" customFormat="1" ht="27" x14ac:dyDescent="0.2">
       <c r="A14" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -9039,10 +9105,10 @@
     </row>
     <row r="15" spans="1:17" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -9062,10 +9128,10 @@
     </row>
     <row r="16" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -9085,10 +9151,10 @@
     </row>
     <row r="17" spans="1:17" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -9108,10 +9174,10 @@
     </row>
     <row r="18" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -9131,10 +9197,10 @@
     </row>
     <row r="19" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -9154,10 +9220,10 @@
     </row>
     <row r="20" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -9177,10 +9243,10 @@
     </row>
     <row r="21" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -9200,10 +9266,10 @@
     </row>
     <row r="22" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -9223,10 +9289,10 @@
     </row>
     <row r="23" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>142</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>143</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -9246,10 +9312,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -9269,10 +9335,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -9290,21 +9356,44 @@
       <c r="P25" s="17"/>
       <c r="Q25" s="17"/>
     </row>
-    <row r="26" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
+    <row r="26" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>448</v>
+      </c>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+    </row>
+    <row r="27" spans="1:17" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A14:F14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9322,10 +9411,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
@@ -9333,16 +9422,16 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>18.75</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H12" s="35"/>
       <c r="J12" s="35"/>
@@ -9350,19 +9439,19 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" t="s">
         <v>105</v>
       </c>
-      <c r="D13" t="s">
-        <v>106</v>
-      </c>
       <c r="E13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G13" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" t="s">
         <v>113</v>
-      </c>
-      <c r="H13" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
@@ -9378,7 +9467,7 @@
         <v>18.75</v>
       </c>
       <c r="G14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -9397,7 +9486,7 @@
         <v>18.75</v>
       </c>
       <c r="G15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H15">
         <v>1.5</v>
@@ -9416,7 +9505,7 @@
         <v>18.75</v>
       </c>
       <c r="G16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -9435,7 +9524,7 @@
         <v>18.75</v>
       </c>
       <c r="G17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H17">
         <v>1.5</v>
@@ -9454,7 +9543,7 @@
         <v>18.75</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H18">
         <v>1</v>

--- a/Data/Hero/角色列表.xlsx
+++ b/Data/Hero/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\Data\Hero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D78144-F394-4D2E-A59F-E7D3C3B58599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5E2F3B-A942-48B0-BA27-07F0F5266035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="60" yWindow="3705" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="451">
   <si>
     <t>No.</t>
   </si>
@@ -1441,38 +1441,6 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>死亡时，对相邻的所有单位（含己方队友）造成</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>点伤害。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
       <t>移动后，可在附近格子放置一颗炸弹。炸弹人以外的角色如果停留在该格就会引爆，受到</t>
     </r>
     <r>
@@ -3198,6 +3166,42 @@
         <family val="2"/>
       </rPr>
       <t>]</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>涌电技师、影丸、火枪手、沉默术士、坠炮手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>死亡时，对相邻的敌方单位造成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>点伤害。</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3898,7 +3902,7 @@
         <v>153</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -3971,7 +3975,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>15</v>
@@ -4005,7 +4009,7 @@
         <v>155</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4051,16 +4055,18 @@
         <f>N4*2.2</f>
         <v>6.6000000000000005</v>
       </c>
-      <c r="P4" s="10"/>
+      <c r="P4" s="10">
+        <v>1</v>
+      </c>
       <c r="Q4" s="10">
         <f t="shared" si="2"/>
-        <v>18.250000000000004</v>
+        <v>19.250000000000004</v>
       </c>
       <c r="R4" s="10" t="s">
         <v>163</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4131,7 +4137,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>21</v>
@@ -4162,7 +4168,7 @@
         <v>155</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="45" x14ac:dyDescent="0.2">
@@ -4287,7 +4293,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>28</v>
@@ -4319,7 +4325,7 @@
         <v>155</v>
       </c>
       <c r="S9" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15" x14ac:dyDescent="0.2">
@@ -4420,7 +4426,7 @@
         <v>163</v>
       </c>
       <c r="S11" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4742,13 +4748,13 @@
         <v>17</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>48</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -4777,7 +4783,7 @@
         <v>163</v>
       </c>
       <c r="S18" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -4887,7 +4893,7 @@
         <v>155</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="57" x14ac:dyDescent="0.2">
@@ -4907,16 +4913,16 @@
         <v>19</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
@@ -4996,7 +5002,7 @@
         <v>155</v>
       </c>
       <c r="S22" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5019,7 +5025,7 @@
         <v>33</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="11"/>
@@ -5076,7 +5082,7 @@
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="11" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="10">
@@ -5123,7 +5129,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
@@ -5173,7 +5179,7 @@
         <v>33</v>
       </c>
       <c r="G26" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="28" t="s">
@@ -5272,7 +5278,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G28" s="20" t="s">
         <v>67</v>
@@ -5306,7 +5312,7 @@
         <v>155</v>
       </c>
       <c r="S28" s="27" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="103.5" x14ac:dyDescent="0.2">
@@ -5327,7 +5333,7 @@
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>122</v>
@@ -5359,7 +5365,7 @@
         <v>163</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5461,7 +5467,7 @@
         <v>163</v>
       </c>
       <c r="S31" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="17.25" x14ac:dyDescent="0.2">
@@ -5484,7 +5490,7 @@
         <v>74</v>
       </c>
       <c r="G32" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
@@ -5583,7 +5589,7 @@
         <v>20</v>
       </c>
       <c r="G34" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>77</v>
@@ -5614,7 +5620,7 @@
         <v>163</v>
       </c>
       <c r="S34" s="27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="71.25" x14ac:dyDescent="0.2">
@@ -5643,7 +5649,7 @@
         <v>124</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
@@ -5692,10 +5698,10 @@
         <v>20</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
@@ -5724,7 +5730,7 @@
         <v>163</v>
       </c>
       <c r="S36" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
@@ -5795,10 +5801,10 @@
       </c>
       <c r="F38" s="9"/>
       <c r="G38" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -5827,7 +5833,7 @@
         <v>163</v>
       </c>
       <c r="S38" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.2">
@@ -5930,7 +5936,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="34.5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -5948,11 +5954,13 @@
       </c>
       <c r="F41" s="9"/>
       <c r="G41" s="21" t="s">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="H41" s="11"/>
       <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="J41" s="11" t="s">
+        <v>449</v>
+      </c>
       <c r="K41" s="9"/>
       <c r="L41" s="10">
         <f t="shared" si="4"/>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="F42" s="9"/>
       <c r="G42" s="21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>57</v>
@@ -6027,7 +6035,7 @@
         <v>155</v>
       </c>
       <c r="S42" s="27" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="51.75" x14ac:dyDescent="0.2">
@@ -6100,7 +6108,7 @@
         <v>20</v>
       </c>
       <c r="G44" s="21" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9"/>
@@ -6156,7 +6164,7 @@
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="9"/>
@@ -6254,11 +6262,11 @@
         <v>95</v>
       </c>
       <c r="G47" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="28" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J47" s="9"/>
       <c r="K47" s="9"/>
@@ -6338,7 +6346,7 @@
         <v>163</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="28.5" x14ac:dyDescent="0.2">
@@ -6349,7 +6357,7 @@
         <v>161</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -6361,7 +6369,7 @@
         <v>33</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H49" s="11"/>
       <c r="I49" s="9"/>
@@ -6399,7 +6407,7 @@
         <v>159</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D50" s="4">
         <v>2</v>
@@ -6411,11 +6419,11 @@
         <v>33</v>
       </c>
       <c r="G50" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
@@ -6582,10 +6590,10 @@
         <v>153</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T1" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6593,10 +6601,10 @@
         <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D2">
         <v>3</v>
@@ -6608,13 +6616,13 @@
         <v>20</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H2" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J2" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L2">
         <v>15.6</v>
@@ -6632,13 +6640,13 @@
         <v>17.8</v>
       </c>
       <c r="R2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S2" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6646,10 +6654,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -6658,13 +6666,13 @@
         <v>24</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H3" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L3">
         <v>15.2</v>
@@ -6682,13 +6690,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -6696,10 +6704,10 @@
         <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -6711,16 +6719,16 @@
         <v>33</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H4" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="J4" s="28" t="s">
         <v>240</v>
-      </c>
-      <c r="J4" s="28" t="s">
-        <v>241</v>
       </c>
       <c r="L4">
         <v>15.2</v>
@@ -6738,13 +6746,13 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S4" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6752,10 +6760,10 @@
         <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -6764,13 +6772,13 @@
         <v>16</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L5">
         <v>16</v>
@@ -6788,13 +6796,13 @@
         <v>19.3</v>
       </c>
       <c r="R5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S5" s="28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6802,10 +6810,10 @@
         <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -6814,13 +6822,13 @@
         <v>20</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L6">
         <v>15.6</v>
@@ -6838,13 +6846,13 @@
         <v>17.8</v>
       </c>
       <c r="R6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S6" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="T6" t="s">
         <v>348</v>
-      </c>
-      <c r="T6" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6852,10 +6860,10 @@
         <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -6864,13 +6872,13 @@
         <v>18</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L7">
         <v>14.7</v>
@@ -6888,13 +6896,13 @@
         <v>18</v>
       </c>
       <c r="R7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S7" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="T7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6902,10 +6910,10 @@
         <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -6914,13 +6922,13 @@
         <v>17</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L8">
         <v>16.45</v>
@@ -6938,13 +6946,13 @@
         <v>18.649999999999999</v>
       </c>
       <c r="R8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S8" s="28" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="T8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -6952,10 +6960,10 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -6964,16 +6972,16 @@
         <v>20</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H9" s="28" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="28" t="s">
+        <v>246</v>
+      </c>
+      <c r="J9" s="28" t="s">
         <v>247</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>248</v>
       </c>
       <c r="L9">
         <v>15.6</v>
@@ -6991,13 +6999,13 @@
         <v>20</v>
       </c>
       <c r="R9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S9" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7005,10 +7013,10 @@
         <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -7020,13 +7028,13 @@
         <v>20</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="H10" s="28" t="s">
-        <v>313</v>
-      </c>
       <c r="J10" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L10">
         <v>14.3</v>
@@ -7044,13 +7052,13 @@
         <v>18.7</v>
       </c>
       <c r="R10" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S10" s="28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7058,10 +7066,10 @@
         <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -7073,13 +7081,13 @@
         <v>20</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J11" s="28" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L11">
         <v>14.7</v>
@@ -7097,13 +7105,13 @@
         <v>18</v>
       </c>
       <c r="R11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S11" s="28" t="s">
+        <v>357</v>
+      </c>
+      <c r="T11" t="s">
         <v>358</v>
-      </c>
-      <c r="T11" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
@@ -7111,10 +7119,10 @@
         <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -7126,13 +7134,13 @@
         <v>14</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J12" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L12">
         <v>16</v>
@@ -7150,13 +7158,13 @@
         <v>19.7</v>
       </c>
       <c r="R12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S12" s="28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="T12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7164,10 +7172,10 @@
         <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D13">
         <v>4</v>
@@ -7179,13 +7187,13 @@
         <v>14</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J13" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L13">
         <v>16.899999999999999</v>
@@ -7203,13 +7211,13 @@
         <v>19.3</v>
       </c>
       <c r="R13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S13" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="T13" t="s">
         <v>364</v>
-      </c>
-      <c r="T13" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7217,10 +7225,10 @@
         <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -7229,16 +7237,16 @@
         <v>20</v>
       </c>
       <c r="G14" s="28" t="s">
+        <v>366</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="I14" s="28" t="s">
         <v>367</v>
       </c>
-      <c r="H14" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="I14" s="28" t="s">
-        <v>368</v>
-      </c>
       <c r="J14" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L14">
         <v>15.6</v>
@@ -7256,13 +7264,13 @@
         <v>17.8</v>
       </c>
       <c r="R14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S14" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="T14" t="s">
         <v>369</v>
-      </c>
-      <c r="T14" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7270,10 +7278,10 @@
         <v>67</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -7285,13 +7293,13 @@
         <v>74</v>
       </c>
       <c r="G15" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="J15" s="28" t="s">
         <v>300</v>
-      </c>
-      <c r="J15" s="28" t="s">
-        <v>301</v>
       </c>
       <c r="L15">
         <v>14.25</v>
@@ -7309,13 +7317,13 @@
         <v>19.649999999999999</v>
       </c>
       <c r="R15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S15" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T15" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7323,10 +7331,10 @@
         <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C16" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D16">
         <v>3</v>
@@ -7335,13 +7343,13 @@
         <v>22</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H16" s="28" t="s">
         <v>57</v>
       </c>
       <c r="J16" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L16">
         <v>16.5</v>
@@ -7359,13 +7367,13 @@
         <v>18.7</v>
       </c>
       <c r="R16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S16" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T16" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7373,10 +7381,10 @@
         <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -7385,13 +7393,13 @@
         <v>18</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H17" s="28" t="s">
+        <v>321</v>
+      </c>
+      <c r="J17" s="28" t="s">
         <v>322</v>
-      </c>
-      <c r="J17" s="28" t="s">
-        <v>323</v>
       </c>
       <c r="L17">
         <v>14.7</v>
@@ -7409,13 +7417,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R17" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S17" s="28" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="T17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7423,10 +7431,10 @@
         <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -7435,13 +7443,13 @@
         <v>24</v>
       </c>
       <c r="G18" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="H18" s="28" t="s">
         <v>378</v>
       </c>
-      <c r="H18" s="28" t="s">
-        <v>379</v>
-      </c>
       <c r="J18" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L18">
         <v>15.2</v>
@@ -7459,13 +7467,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S18" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="T18" t="s">
         <v>380</v>
-      </c>
-      <c r="T18" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7473,10 +7481,10 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C19" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -7485,13 +7493,13 @@
         <v>22</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H19" s="28" t="s">
         <v>28</v>
       </c>
       <c r="J19" s="28" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L19">
         <v>16.5</v>
@@ -7509,13 +7517,13 @@
         <v>18.7</v>
       </c>
       <c r="R19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S19" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7523,10 +7531,10 @@
         <v>72</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C20" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -7535,13 +7543,13 @@
         <v>26</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H20" s="28" t="s">
         <v>26</v>
       </c>
       <c r="J20" s="28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L20">
         <v>16.100000000000001</v>
@@ -7559,13 +7567,13 @@
         <v>18.3</v>
       </c>
       <c r="R20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S20" s="28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="T20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7573,10 +7581,10 @@
         <v>73</v>
       </c>
       <c r="B21" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7588,13 +7596,13 @@
         <v>20</v>
       </c>
       <c r="G21" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="H21" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="I21" s="28" t="s">
         <v>269</v>
-      </c>
-      <c r="I21" s="28" t="s">
-        <v>270</v>
       </c>
       <c r="J21" s="28" t="s">
         <v>90</v>
@@ -7615,13 +7623,13 @@
         <v>19.2</v>
       </c>
       <c r="R21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S21" s="28" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="171" x14ac:dyDescent="0.2">
@@ -7629,10 +7637,10 @@
         <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -7641,16 +7649,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="H22" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="I22" s="28" t="s">
-        <v>392</v>
-      </c>
       <c r="J22" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L22">
         <v>15.2</v>
@@ -7668,13 +7676,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S22" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T22" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -7682,10 +7690,10 @@
         <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -7697,13 +7705,13 @@
         <v>33</v>
       </c>
       <c r="G23" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="H23" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="H23" s="28" t="s">
-        <v>396</v>
-      </c>
       <c r="J23" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L23">
         <v>17.899999999999999</v>
@@ -7721,13 +7729,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S23" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T23" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7735,10 +7743,10 @@
         <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C24" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -7750,16 +7758,16 @@
         <v>33</v>
       </c>
       <c r="G24" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="H24" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="I24" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>252</v>
-      </c>
       <c r="J24" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L24">
         <v>16.149999999999999</v>
@@ -7777,13 +7785,13 @@
         <v>19.55</v>
       </c>
       <c r="R24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S24" s="28" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="T24" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="57" x14ac:dyDescent="0.2">
@@ -7791,10 +7799,10 @@
         <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C25" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -7803,16 +7811,16 @@
         <v>26</v>
       </c>
       <c r="G25" s="28" t="s">
+        <v>400</v>
+      </c>
+      <c r="H25" s="28" t="s">
         <v>401</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="I25" s="28" t="s">
         <v>402</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="J25" s="28" t="s">
         <v>403</v>
-      </c>
-      <c r="J25" s="28" t="s">
-        <v>404</v>
       </c>
       <c r="L25">
         <v>16.100000000000001</v>
@@ -7830,13 +7838,13 @@
         <v>18.3</v>
       </c>
       <c r="R25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S25" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T25" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="57" x14ac:dyDescent="0.2">
@@ -7844,10 +7852,10 @@
         <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -7859,16 +7867,16 @@
         <v>33</v>
       </c>
       <c r="G26" s="28" t="s">
+        <v>331</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="I26" s="28" t="s">
+        <v>405</v>
+      </c>
+      <c r="J26" s="28" t="s">
         <v>332</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>406</v>
-      </c>
-      <c r="J26" s="28" t="s">
-        <v>333</v>
       </c>
       <c r="L26">
         <v>17.899999999999999</v>
@@ -7886,13 +7894,13 @@
         <v>18.25</v>
       </c>
       <c r="R26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S26" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="T26" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="27" spans="1:20" ht="85.5" x14ac:dyDescent="0.2">
@@ -7900,10 +7908,10 @@
         <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -7912,16 +7920,16 @@
         <v>22</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H27" s="28" t="s">
         <v>28</v>
       </c>
       <c r="I27" s="28" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J27" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L27">
         <v>14.3</v>
@@ -7939,13 +7947,13 @@
         <v>18.7</v>
       </c>
       <c r="R27" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S27" s="28" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T27" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -7953,10 +7961,10 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C28" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -7968,16 +7976,16 @@
         <v>33</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H28" s="28" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L28">
         <v>16.600000000000001</v>
@@ -7995,13 +8003,13 @@
         <v>17.8</v>
       </c>
       <c r="R28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S28" s="28" t="s">
+        <v>409</v>
+      </c>
+      <c r="T28" t="s">
         <v>410</v>
-      </c>
-      <c r="T28" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8009,10 +8017,10 @@
         <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -8024,13 +8032,13 @@
         <v>33</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H29" s="28" t="s">
         <v>57</v>
       </c>
       <c r="J29" s="28" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L29">
         <v>17.899999999999999</v>
@@ -8048,13 +8056,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S29" s="28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="T29" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8062,10 +8070,10 @@
         <v>82</v>
       </c>
       <c r="B30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C30" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -8077,13 +8085,13 @@
         <v>33</v>
       </c>
       <c r="G30" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="H30" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="J30" s="28" t="s">
         <v>284</v>
-      </c>
-      <c r="J30" s="28" t="s">
-        <v>285</v>
       </c>
       <c r="L30">
         <v>17.95</v>
@@ -8101,13 +8109,13 @@
         <v>19.2</v>
       </c>
       <c r="R30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S30" s="28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="T30" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8115,10 +8123,10 @@
         <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C31" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -8130,13 +8138,13 @@
         <v>33</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H31" s="28" t="s">
         <v>28</v>
       </c>
       <c r="J31" s="28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L31">
         <v>15.2</v>
@@ -8154,13 +8162,13 @@
         <v>18.600000000000001</v>
       </c>
       <c r="R31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S31" s="28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="T31" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:20" ht="42.75" x14ac:dyDescent="0.2">
@@ -8168,10 +8176,10 @@
         <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -8183,16 +8191,16 @@
         <v>33</v>
       </c>
       <c r="G32" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="H32" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="H32" s="28" t="s">
+      <c r="I32" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="J32" s="28" t="s">
         <v>308</v>
-      </c>
-      <c r="J32" s="28" t="s">
-        <v>309</v>
       </c>
       <c r="L32">
         <v>18.399999999999999</v>
@@ -8210,13 +8218,13 @@
         <v>18.75</v>
       </c>
       <c r="R32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="T32" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8224,10 +8232,10 @@
         <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D33">
         <v>2</v>
@@ -8239,13 +8247,13 @@
         <v>33</v>
       </c>
       <c r="G33" s="28" t="s">
+        <v>327</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="J33" s="28" t="s">
         <v>328</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>300</v>
-      </c>
-      <c r="J33" s="28" t="s">
-        <v>329</v>
       </c>
       <c r="L33">
         <v>17.899999999999999</v>
@@ -8263,13 +8271,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="S33" s="28" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="T33" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="114" x14ac:dyDescent="0.2">
@@ -8277,10 +8285,10 @@
         <v>86</v>
       </c>
       <c r="B34" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" t="s">
         <v>256</v>
-      </c>
-      <c r="C34" t="s">
-        <v>257</v>
       </c>
       <c r="D34">
         <v>2</v>
@@ -8292,16 +8300,16 @@
         <v>20</v>
       </c>
       <c r="G34" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="H34" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="I34" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="J34" s="28" t="s">
         <v>260</v>
-      </c>
-      <c r="J34" s="28" t="s">
-        <v>261</v>
       </c>
       <c r="L34">
         <v>12.5</v>
@@ -8319,13 +8327,13 @@
         <v>19.100000000000001</v>
       </c>
       <c r="R34" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S34" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T34" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35" spans="1:20" ht="99.75" x14ac:dyDescent="0.2">
@@ -8333,10 +8341,10 @@
         <v>87</v>
       </c>
       <c r="B35" t="s">
+        <v>271</v>
+      </c>
+      <c r="C35" t="s">
         <v>272</v>
-      </c>
-      <c r="C35" t="s">
-        <v>273</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -8345,16 +8353,16 @@
         <v>21</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H35" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="I35" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="J35" s="28" t="s">
         <v>275</v>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>276</v>
       </c>
       <c r="L35">
         <v>13.85</v>
@@ -8372,13 +8380,13 @@
         <v>18.25</v>
       </c>
       <c r="R35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="S35" s="28" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="36" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8386,10 +8394,10 @@
         <v>88</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C36" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -8401,13 +8409,13 @@
         <v>20</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H36" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J36" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L36">
         <v>17</v>
@@ -8425,13 +8433,13 @@
         <v>18.350000000000001</v>
       </c>
       <c r="R36" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S36" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T36" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8439,10 +8447,10 @@
         <v>89</v>
       </c>
       <c r="B37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C37" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D37">
         <v>2</v>
@@ -8451,13 +8459,13 @@
         <v>24</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H37" s="28" t="s">
+        <v>290</v>
+      </c>
+      <c r="J37" s="28" t="s">
         <v>291</v>
-      </c>
-      <c r="J37" s="28" t="s">
-        <v>292</v>
       </c>
       <c r="L37">
         <v>15.2</v>
@@ -8475,13 +8483,13 @@
         <v>19.600000000000001</v>
       </c>
       <c r="R37" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S37" s="28" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="T37" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8489,10 +8497,10 @@
         <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C38" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -8504,13 +8512,13 @@
         <v>20</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H38" s="28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J38" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L38">
         <v>15.7</v>
@@ -8528,13 +8536,13 @@
         <v>19</v>
       </c>
       <c r="R38" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S38" s="28" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T38" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8542,10 +8550,10 @@
         <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -8554,13 +8562,13 @@
         <v>20</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H39" s="28" t="s">
         <v>53</v>
       </c>
       <c r="J39" s="28" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L39">
         <v>15.6</v>
@@ -8578,13 +8586,13 @@
         <v>18.899999999999999</v>
       </c>
       <c r="R39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S39" s="28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="T39" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8592,10 +8600,10 @@
         <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D40">
         <v>6</v>
@@ -8608,7 +8616,7 @@
         <v>26</v>
       </c>
       <c r="J40" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L40">
         <v>19.05</v>
@@ -8626,13 +8634,13 @@
         <v>19.05</v>
       </c>
       <c r="R40" t="s">
+        <v>234</v>
+      </c>
+      <c r="S40" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="S40" s="28" t="s">
-        <v>236</v>
-      </c>
       <c r="T40" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8640,10 +8648,10 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D41">
         <v>5</v>
@@ -8658,7 +8666,7 @@
         <v>26</v>
       </c>
       <c r="J41" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L41">
         <v>17.3</v>
@@ -8676,13 +8684,13 @@
         <v>18.8</v>
       </c>
       <c r="R41" t="s">
+        <v>234</v>
+      </c>
+      <c r="S41" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="S41" s="28" t="s">
-        <v>236</v>
-      </c>
       <c r="T41" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
@@ -8690,10 +8698,10 @@
         <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D42">
         <v>5</v>
@@ -8708,7 +8716,7 @@
         <v>26</v>
       </c>
       <c r="J42" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L42">
         <v>16.850000000000001</v>
@@ -8726,13 +8734,13 @@
         <v>18.350000000000001</v>
       </c>
       <c r="R42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S42" s="28" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="T42" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.2">
@@ -8740,10 +8748,10 @@
         <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -8758,7 +8766,7 @@
         <v>26</v>
       </c>
       <c r="J43" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L43">
         <v>18.7</v>
@@ -8776,13 +8784,13 @@
         <v>18.7</v>
       </c>
       <c r="R43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S43" s="28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T43" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>
@@ -8798,16 +8806,16 @@
   <sheetData>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B5" s="30"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -8860,15 +8868,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B14" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A14)</f>
@@ -8877,7 +8885,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B15" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A15)</f>
@@ -8886,7 +8894,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="3">
         <f>COUNTIF(角色列表!R:R,数据统计!A16)</f>
@@ -9131,7 +9139,7 @@
         <v>134</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -9154,7 +9162,7 @@
         <v>135</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -9177,7 +9185,7 @@
         <v>136</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -9200,7 +9208,7 @@
         <v>137</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -9223,7 +9231,7 @@
         <v>138</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -9269,7 +9277,7 @@
         <v>140</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -9312,10 +9320,10 @@
     </row>
     <row r="24" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -9335,10 +9343,10 @@
     </row>
     <row r="25" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -9358,10 +9366,10 @@
     </row>
     <row r="26" spans="1:17" s="7" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
